--- a/Visao_BID_Comunicacao_com_estimativa.xlsx
+++ b/Visao_BID_Comunicacao_com_estimativa.xlsx
@@ -53,7 +53,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>-1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -86,7 +86,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:rowOff>-4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -119,7 +119,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:rowOff>-4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -152,7 +152,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:rowOff>-4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -337,7 +337,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:rowOff>-1</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -370,7 +370,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:rowOff>-4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -403,7 +403,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:rowOff>-4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -436,7 +436,7 @@
                 <xdr:col>1</xdr:col>
                 <xdr:colOff>-176</xdr:colOff>
                 <xdr:row>1</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:rowOff>-4</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -449,7 +449,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="90">
   <si>
     <t xml:space="preserve">Fornecedores</t>
   </si>
@@ -544,7 +544,13 @@
     <t xml:space="preserve">Fornecedor Menor Preço</t>
   </si>
   <si>
-    <t xml:space="preserve">Qtd anual estimada (base 2025)</t>
+    <t xml:space="preserve">Qtd anual estimada (TOTAL)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Monday (jobs 2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Calendário canais internos 2025 (jan–dez)</t>
   </si>
   <si>
     <t xml:space="preserve">ExtraFee</t>
@@ -713,15 +719,6 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Qtd anual estimada (TOTAL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Monday (jobs 2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+ Calendário canais internos 2025 (jan–dez)</t>
   </si>
 </sst>
 </file>
@@ -929,7 +926,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1018,7 +1015,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1058,10 +1055,6 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="10" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="0" fillId="12" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1087,10 +1080,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="11" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1642,7 +1631,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C25960EA-5C25-4FF2-8F32-FF5050AEC23C}</x14:id>
+          <x14:id>{6EF59C1C-22FC-4FB0-B430-D8EE41EDA4E1}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1668,7 +1657,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C25960EA-5C25-4FF2-8F32-FF5050AEC23C}">
+          <x14:cfRule type="dataBar" id="{6EF59C1C-22FC-4FB0-B430-D8EE41EDA4E1}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="none" gradient="true">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -1689,7 +1678,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.14"/>
@@ -1700,11 +1689,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="2.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="12" style="1" width="10.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -1755,10 +1745,16 @@
       <c r="R1" s="11" t="s">
         <v>32</v>
       </c>
+      <c r="S1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="16" t="n">
         <v>4364</v>
@@ -1802,15 +1798,22 @@
         <v>-0.435838680109991</v>
       </c>
       <c r="Q2" s="22" t="n">
+        <f aca="false">R2+S2</f>
+        <v>511</v>
+      </c>
+      <c r="R2" s="22" t="n">
         <v>120</v>
       </c>
-      <c r="R2" s="22" t="n">
+      <c r="S2" s="22" t="n">
+        <v>391</v>
+      </c>
+      <c r="T2" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="16" t="n">
         <v>5866</v>
@@ -1854,15 +1857,22 @@
         <v>-0.460961472894647</v>
       </c>
       <c r="Q3" s="22" t="n">
+        <f aca="false">R3+S3</f>
         <v>56</v>
       </c>
       <c r="R3" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="S3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>8729</v>
@@ -1906,15 +1916,22 @@
         <v>-0.381372436705236</v>
       </c>
       <c r="Q4" s="22" t="n">
+        <f aca="false">R4+S4</f>
         <v>0</v>
       </c>
       <c r="R4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>4364</v>
@@ -1958,15 +1975,22 @@
         <v>-0.564619615032081</v>
       </c>
       <c r="Q5" s="22" t="n">
+        <f aca="false">R5+S5</f>
         <v>0</v>
       </c>
       <c r="R5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>6546</v>
@@ -2010,15 +2034,22 @@
         <v>-0.306446684998472</v>
       </c>
       <c r="Q6" s="22" t="n">
+        <f aca="false">R6+S6</f>
         <v>0</v>
       </c>
       <c r="R6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>844</v>
@@ -2062,15 +2093,22 @@
         <v>-0.333329383886256</v>
       </c>
       <c r="Q7" s="22" t="n">
+        <f aca="false">R7+S7</f>
+        <v>579</v>
+      </c>
+      <c r="R7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="R7" s="22" t="n">
+      <c r="S7" s="22" t="n">
+        <v>576</v>
+      </c>
+      <c r="T7" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>7946</v>
@@ -2112,15 +2150,22 @@
         <v>-1</v>
       </c>
       <c r="Q8" s="22" t="n">
+        <f aca="false">R8+S8</f>
         <v>0</v>
       </c>
       <c r="R8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>13554</v>
@@ -2164,15 +2209,22 @@
         <v>-0.350745167478235</v>
       </c>
       <c r="Q9" s="22" t="n">
+        <f aca="false">R9+S9</f>
         <v>17</v>
       </c>
       <c r="R9" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="S9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>27108</v>
@@ -2216,15 +2268,22 @@
         <v>-0.0482514386896857</v>
       </c>
       <c r="Q10" s="22" t="n">
+        <f aca="false">R10+S10</f>
         <v>5</v>
       </c>
       <c r="R10" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>14545</v>
@@ -2268,15 +2327,22 @@
         <v>-0.174974217944311</v>
       </c>
       <c r="Q11" s="22" t="n">
+        <f aca="false">R11+S11</f>
         <v>0</v>
       </c>
       <c r="R11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>11785</v>
@@ -2320,15 +2386,22 @@
         <v>-0.330504879083581</v>
       </c>
       <c r="Q12" s="22" t="n">
+        <f aca="false">R12+S12</f>
         <v>0</v>
       </c>
       <c r="R12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>117535</v>
@@ -2372,15 +2445,22 @@
         <v>-0.787297400774238</v>
       </c>
       <c r="Q13" s="22" t="n">
+        <f aca="false">R13+S13</f>
         <v>1</v>
       </c>
       <c r="R13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>58768</v>
@@ -2424,15 +2504,22 @@
         <v>-0.782194391505581</v>
       </c>
       <c r="Q14" s="22" t="n">
+        <f aca="false">R14+S14</f>
         <v>8</v>
       </c>
       <c r="R14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>41136</v>
@@ -2476,15 +2563,22 @@
         <v>-0.787047841306884</v>
       </c>
       <c r="Q15" s="22" t="n">
+        <f aca="false">R15+S15</f>
         <v>17</v>
       </c>
       <c r="R15" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="S15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>41136</v>
@@ -2528,15 +2622,22 @@
         <v>-0.0942726565538701</v>
       </c>
       <c r="Q16" s="22" t="n">
+        <f aca="false">R16+S16</f>
         <v>0</v>
       </c>
       <c r="R16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>58766</v>
@@ -2580,15 +2681,22 @@
         <v>-0.0880441071367798</v>
       </c>
       <c r="Q17" s="22" t="n">
+        <f aca="false">R17+S17</f>
         <v>1</v>
       </c>
       <c r="R17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>29383</v>
@@ -2632,15 +2740,22 @@
         <v>-0.109246843412858</v>
       </c>
       <c r="Q18" s="22" t="n">
+        <f aca="false">R18+S18</f>
         <v>0</v>
       </c>
       <c r="R18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>25754</v>
@@ -2684,15 +2799,22 @@
         <v>-0.479692474955347</v>
       </c>
       <c r="Q19" s="22" t="n">
+        <f aca="false">R19+S19</f>
         <v>10</v>
       </c>
       <c r="R19" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="16" t="n">
         <v>20767</v>
@@ -2736,15 +2858,22 @@
         <v>-0.0610102566571965</v>
       </c>
       <c r="Q20" s="22" t="n">
+        <f aca="false">R20+S20</f>
         <v>1</v>
       </c>
       <c r="R20" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" s="16" t="n">
         <v>14692</v>
@@ -2788,15 +2917,22 @@
         <v>-0.714130138851076</v>
       </c>
       <c r="Q21" s="22" t="n">
+        <f aca="false">R21+S21</f>
         <v>4</v>
       </c>
       <c r="R21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" s="16" t="n">
         <v>11455</v>
@@ -2840,15 +2976,22 @@
         <v>-0.75556525534701</v>
       </c>
       <c r="Q22" s="22" t="n">
+        <f aca="false">R22+S22</f>
         <v>4</v>
       </c>
       <c r="R22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="16" t="n">
         <v>6615</v>
@@ -2892,15 +3035,22 @@
         <v>0.647770219198791</v>
       </c>
       <c r="Q23" s="22" t="n">
+        <f aca="false">R23+S23</f>
         <v>12</v>
       </c>
       <c r="R23" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="16" t="n">
         <v>5715</v>
@@ -2944,15 +3094,22 @@
         <v>-0.617322834645669</v>
       </c>
       <c r="Q24" s="22" t="n">
+        <f aca="false">R24+S24</f>
         <v>35</v>
       </c>
       <c r="R24" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="S24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="16" t="n">
         <v>4572</v>
@@ -2996,15 +3153,22 @@
         <v>-0.628171478565179</v>
       </c>
       <c r="Q25" s="22" t="n">
+        <f aca="false">R25+S25</f>
         <v>13</v>
       </c>
       <c r="R25" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="16" t="n">
         <v>8868</v>
@@ -3048,15 +3212,22 @@
         <v>-0.588971583220568</v>
       </c>
       <c r="Q26" s="22" t="n">
+        <f aca="false">R26+S26</f>
         <v>15</v>
       </c>
       <c r="R26" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="S26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="16" t="n">
         <v>7122</v>
@@ -3100,15 +3271,22 @@
         <v>-0.0452120190957597</v>
       </c>
       <c r="Q27" s="22" t="n">
+        <f aca="false">R27+S27</f>
         <v>0</v>
       </c>
       <c r="R27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="16" t="n">
         <v>3824</v>
@@ -3152,15 +3330,22 @@
         <v>-0.364539748953975</v>
       </c>
       <c r="Q28" s="22" t="n">
+        <f aca="false">R28+S28</f>
+        <v>32</v>
+      </c>
+      <c r="R28" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="R28" s="22" t="n">
+      <c r="S28" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="T28" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" s="16" t="n">
         <v>11904</v>
@@ -3204,15 +3389,22 @@
         <v>-0.479166666666667</v>
       </c>
       <c r="Q29" s="22" t="n">
+        <f aca="false">R29+S29</f>
         <v>6</v>
       </c>
       <c r="R29" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="S29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" s="16" t="n">
         <v>4216</v>
@@ -3256,15 +3448,22 @@
         <v>-0.743833017077799</v>
       </c>
       <c r="Q30" s="22" t="n">
+        <f aca="false">R30+S30</f>
         <v>0</v>
       </c>
       <c r="R30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" s="16" t="n">
         <v>25684</v>
@@ -3308,15 +3507,22 @@
         <v>-0.264133312568136</v>
       </c>
       <c r="Q31" s="22" t="n">
+        <f aca="false">R31+S31</f>
         <v>3</v>
       </c>
       <c r="R31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" s="16" t="n">
         <v>5137</v>
@@ -3360,15 +3566,22 @@
         <v>-0.828693790149893</v>
       </c>
       <c r="Q32" s="22" t="n">
+        <f aca="false">R32+S32</f>
         <v>0</v>
       </c>
       <c r="R32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B33" s="16" t="n">
         <v>25419</v>
@@ -3412,15 +3625,22 @@
         <v>-0.713206656438097</v>
       </c>
       <c r="Q33" s="22" t="n">
+        <f aca="false">R33+S33</f>
         <v>3</v>
       </c>
       <c r="R33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="16" t="n">
         <v>17696</v>
@@ -3464,15 +3684,22 @@
         <v>-0.313404159132007</v>
       </c>
       <c r="Q34" s="22" t="n">
+        <f aca="false">R34+S34</f>
         <v>0</v>
       </c>
       <c r="R34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B35" s="16" t="n">
         <v>40957</v>
@@ -3516,15 +3743,22 @@
         <v>-0.406694826281222</v>
       </c>
       <c r="Q35" s="22" t="n">
+        <f aca="false">R35+S35</f>
         <v>0</v>
       </c>
       <c r="R35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B36" s="16" t="n">
         <v>19364</v>
@@ -3568,15 +3802,22 @@
         <v>-0.597190663086139</v>
       </c>
       <c r="Q36" s="22" t="n">
+        <f aca="false">R36+S36</f>
         <v>1</v>
       </c>
       <c r="R36" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="S36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B37" s="16" t="n">
         <v>29043</v>
@@ -3620,15 +3861,22 @@
         <v>-0.621251248149296</v>
       </c>
       <c r="Q37" s="22" t="n">
+        <f aca="false">R37+S37</f>
         <v>0</v>
       </c>
       <c r="R37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B38" s="16" t="n">
         <v>29102</v>
@@ -3672,15 +3920,22 @@
         <v>1.06171397154835</v>
       </c>
       <c r="Q38" s="22" t="n">
+        <f aca="false">R38+S38</f>
         <v>12</v>
       </c>
       <c r="R38" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B39" s="16" t="n">
         <v>19364</v>
@@ -3724,15 +3979,22 @@
         <v>-0.338979549679818</v>
       </c>
       <c r="Q39" s="22" t="n">
+        <f aca="false">R39+S39</f>
         <v>0</v>
       </c>
       <c r="R39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B40" s="16" t="n">
         <v>29043</v>
@@ -3776,15 +4038,22 @@
         <v>-0.517956134008195</v>
       </c>
       <c r="Q40" s="22" t="n">
+        <f aca="false">R40+S40</f>
         <v>0</v>
       </c>
       <c r="R40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B41" s="16" t="n">
         <v>12093</v>
@@ -3828,15 +4097,22 @@
         <v>-0.354998759612999</v>
       </c>
       <c r="Q41" s="22" t="n">
+        <f aca="false">R41+S41</f>
         <v>4</v>
       </c>
       <c r="R41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B42" s="16" t="n">
         <v>5678</v>
@@ -3880,15 +4156,22 @@
         <v>-0.144064811553364</v>
       </c>
       <c r="Q42" s="22" t="n">
-        <v>2</v>
+        <f aca="false">R42+S42</f>
+        <v>40</v>
       </c>
       <c r="R42" s="22" t="n">
         <v>2</v>
       </c>
+      <c r="S42" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="T42" s="22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B43" s="16" t="n">
         <v>13020</v>
@@ -3932,15 +4215,22 @@
         <v>-0.585253456221198</v>
       </c>
       <c r="Q43" s="22" t="n">
+        <f aca="false">R43+S43</f>
         <v>0</v>
       </c>
       <c r="R43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B44" s="16" t="n">
         <v>117535</v>
@@ -3984,15 +4274,22 @@
         <v>-0.446973242013017</v>
       </c>
       <c r="Q44" s="22" t="n">
+        <f aca="false">R44+S44</f>
         <v>1</v>
       </c>
       <c r="R44" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="S44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B45" s="16" t="n">
         <v>22729</v>
@@ -4036,15 +4333,22 @@
         <v>-0.208060187425756</v>
       </c>
       <c r="Q45" s="22" t="n">
+        <f aca="false">R45+S45</f>
         <v>5</v>
       </c>
       <c r="R45" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B46" s="16" t="n">
         <v>27699</v>
@@ -4088,15 +4392,22 @@
         <v>-0.205747499909744</v>
       </c>
       <c r="Q46" s="22" t="n">
+        <f aca="false">R46+S46</f>
         <v>0</v>
       </c>
       <c r="R46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B47" s="16" t="n">
         <v>2598</v>
@@ -4140,15 +4451,22 @@
         <v>-0.30715935334873</v>
       </c>
       <c r="Q47" s="22" t="n">
+        <f aca="false">R47+S47</f>
         <v>0</v>
       </c>
       <c r="R47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B48" s="16" t="n">
         <v>18296</v>
@@ -4192,15 +4510,22 @@
         <v>-0.196545693047661</v>
       </c>
       <c r="Q48" s="22" t="n">
+        <f aca="false">R48+S48</f>
         <v>0</v>
       </c>
       <c r="R48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B49" s="16" t="n">
         <v>7858</v>
@@ -4244,15 +4569,22 @@
         <v>0.11987783150929</v>
       </c>
       <c r="Q49" s="22" t="n">
+        <f aca="false">R49+S49</f>
         <v>6</v>
       </c>
       <c r="R49" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B50" s="16" t="n">
         <v>7030</v>
@@ -4296,15 +4628,22 @@
         <v>-0.516358463726885</v>
       </c>
       <c r="Q50" s="22" t="n">
+        <f aca="false">R50+S50</f>
         <v>3</v>
       </c>
       <c r="R50" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B51" s="16" t="n">
         <v>1556</v>
@@ -4348,15 +4687,22 @@
         <v>-0.663714652956298</v>
       </c>
       <c r="Q51" s="22" t="n">
+        <f aca="false">R51+S51</f>
         <v>0</v>
       </c>
       <c r="R51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B52" s="16" t="n">
         <v>1040</v>
@@ -4400,15 +4746,22 @@
         <v>-0.652644230769231</v>
       </c>
       <c r="Q52" s="22" t="n">
+        <f aca="false">R52+S52</f>
         <v>0</v>
       </c>
       <c r="R52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B53" s="16" t="n">
         <v>727</v>
@@ -4452,15 +4805,22 @@
         <v>-0.722943603851444</v>
       </c>
       <c r="Q53" s="22" t="n">
+        <f aca="false">R53+S53</f>
         <v>0</v>
       </c>
       <c r="R53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B54" s="16" t="n">
         <v>779</v>
@@ -4504,15 +4864,22 @@
         <v>-0.165596919127086</v>
       </c>
       <c r="Q54" s="22" t="n">
+        <f aca="false">R54+S54</f>
         <v>0</v>
       </c>
       <c r="R54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B55" s="16" t="n">
         <v>28000</v>
@@ -4556,15 +4923,22 @@
         <v>89568</v>
       </c>
       <c r="Q55" s="22" t="n">
+        <f aca="false">R55+S55</f>
         <v>12</v>
       </c>
       <c r="R55" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B56" s="25" t="n">
         <v>1085326</v>
@@ -4645,7 +5019,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="3.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="12" style="1" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="17" style="1" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4694,21 +5068,21 @@
         <v>28</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="S1" s="11" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="28" t="n">
         <v>4364</v>
@@ -4751,23 +5125,23 @@
       <c r="P2" s="21" t="n">
         <v>-0.435838680109991</v>
       </c>
-      <c r="Q2" s="32" t="n">
+      <c r="Q2" s="22" t="n">
         <f aca="false">R2+S2</f>
         <v>511</v>
       </c>
-      <c r="R2" s="32" t="n">
+      <c r="R2" s="22" t="n">
         <v>120</v>
       </c>
-      <c r="S2" s="32" t="n">
+      <c r="S2" s="22" t="n">
         <v>391</v>
       </c>
-      <c r="T2" s="32" t="n">
+      <c r="T2" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="28" t="n">
         <v>5866</v>
@@ -4810,23 +5184,23 @@
       <c r="P3" s="21" t="n">
         <v>-0.460961472894647</v>
       </c>
-      <c r="Q3" s="32" t="n">
+      <c r="Q3" s="22" t="n">
         <f aca="false">R3+S3</f>
         <v>56</v>
       </c>
-      <c r="R3" s="32" t="n">
+      <c r="R3" s="22" t="n">
         <v>56</v>
       </c>
-      <c r="S3" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="32" t="n">
+      <c r="S3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="28" t="n">
         <v>8729</v>
@@ -4869,23 +5243,23 @@
       <c r="P4" s="21" t="n">
         <v>-0.381372436705236</v>
       </c>
-      <c r="Q4" s="32" t="n">
+      <c r="Q4" s="22" t="n">
         <f aca="false">R4+S4</f>
         <v>0</v>
       </c>
-      <c r="R4" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="32" t="n">
+      <c r="R4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="28" t="n">
         <v>4364</v>
@@ -4928,23 +5302,23 @@
       <c r="P5" s="21" t="n">
         <v>-0.564619615032081</v>
       </c>
-      <c r="Q5" s="32" t="n">
+      <c r="Q5" s="22" t="n">
         <f aca="false">R5+S5</f>
         <v>0</v>
       </c>
-      <c r="R5" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="32" t="n">
+      <c r="R5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>6546</v>
@@ -4987,23 +5361,23 @@
       <c r="P6" s="21" t="n">
         <v>-0.306446684998472</v>
       </c>
-      <c r="Q6" s="32" t="n">
+      <c r="Q6" s="22" t="n">
         <f aca="false">R6+S6</f>
         <v>0</v>
       </c>
-      <c r="R6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="32" t="n">
+      <c r="R6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>844</v>
@@ -5046,23 +5420,23 @@
       <c r="P7" s="21" t="n">
         <v>-0.333329383886256</v>
       </c>
-      <c r="Q7" s="32" t="n">
+      <c r="Q7" s="22" t="n">
         <f aca="false">R7+S7</f>
         <v>579</v>
       </c>
-      <c r="R7" s="32" t="n">
+      <c r="R7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="S7" s="32" t="n">
+      <c r="S7" s="22" t="n">
         <v>576</v>
       </c>
-      <c r="T7" s="32" t="n">
+      <c r="T7" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>7946</v>
@@ -5079,7 +5453,7 @@
       <c r="F8" s="29" t="n">
         <v>6000</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="30"/>
       <c r="I8" s="31" t="n">
         <v>2208</v>
@@ -5103,23 +5477,23 @@
       <c r="P8" s="21" t="n">
         <v>-1</v>
       </c>
-      <c r="Q8" s="32" t="n">
+      <c r="Q8" s="22" t="n">
         <f aca="false">R8+S8</f>
         <v>0</v>
       </c>
-      <c r="R8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="32" t="n">
+      <c r="R8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="28" t="n">
         <v>13554</v>
@@ -5162,23 +5536,23 @@
       <c r="P9" s="21" t="n">
         <v>-0.350745167478235</v>
       </c>
-      <c r="Q9" s="32" t="n">
+      <c r="Q9" s="22" t="n">
         <f aca="false">R9+S9</f>
         <v>17</v>
       </c>
-      <c r="R9" s="32" t="n">
+      <c r="R9" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="S9" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="32" t="n">
+      <c r="S9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" s="28" t="n">
         <v>27108</v>
@@ -5221,23 +5595,23 @@
       <c r="P10" s="21" t="n">
         <v>-0.0482514386896857</v>
       </c>
-      <c r="Q10" s="32" t="n">
+      <c r="Q10" s="22" t="n">
         <f aca="false">R10+S10</f>
         <v>5</v>
       </c>
-      <c r="R10" s="32" t="n">
+      <c r="R10" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="S10" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="32" t="n">
+      <c r="S10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" s="28" t="n">
         <v>14545</v>
@@ -5280,23 +5654,23 @@
       <c r="P11" s="21" t="n">
         <v>-0.174974217944311</v>
       </c>
-      <c r="Q11" s="32" t="n">
+      <c r="Q11" s="22" t="n">
         <f aca="false">R11+S11</f>
         <v>0</v>
       </c>
-      <c r="R11" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="32" t="n">
+      <c r="R11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" s="28" t="n">
         <v>11785</v>
@@ -5339,23 +5713,23 @@
       <c r="P12" s="21" t="n">
         <v>-0.330504879083581</v>
       </c>
-      <c r="Q12" s="32" t="n">
+      <c r="Q12" s="22" t="n">
         <f aca="false">R12+S12</f>
         <v>0</v>
       </c>
-      <c r="R12" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="32" t="n">
+      <c r="R12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" s="28" t="n">
         <v>117535</v>
@@ -5398,23 +5772,23 @@
       <c r="P13" s="21" t="n">
         <v>-0.787297400774238</v>
       </c>
-      <c r="Q13" s="32" t="n">
+      <c r="Q13" s="22" t="n">
         <f aca="false">R13+S13</f>
         <v>1</v>
       </c>
-      <c r="R13" s="32" t="n">
+      <c r="R13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="S13" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="32" t="n">
+      <c r="S13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" s="28" t="n">
         <v>58768</v>
@@ -5457,23 +5831,23 @@
       <c r="P14" s="21" t="n">
         <v>-0.782194391505581</v>
       </c>
-      <c r="Q14" s="32" t="n">
+      <c r="Q14" s="22" t="n">
         <f aca="false">R14+S14</f>
         <v>8</v>
       </c>
-      <c r="R14" s="32" t="n">
+      <c r="R14" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="S14" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="32" t="n">
+      <c r="S14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" s="28" t="n">
         <v>41136</v>
@@ -5516,23 +5890,23 @@
       <c r="P15" s="21" t="n">
         <v>-0.787047841306884</v>
       </c>
-      <c r="Q15" s="32" t="n">
+      <c r="Q15" s="22" t="n">
         <f aca="false">R15+S15</f>
         <v>17</v>
       </c>
-      <c r="R15" s="32" t="n">
+      <c r="R15" s="22" t="n">
         <v>17</v>
       </c>
-      <c r="S15" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="32" t="n">
+      <c r="S15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" s="28" t="n">
         <v>41136</v>
@@ -5575,23 +5949,23 @@
       <c r="P16" s="21" t="n">
         <v>-0.0942726565538701</v>
       </c>
-      <c r="Q16" s="32" t="n">
+      <c r="Q16" s="22" t="n">
         <f aca="false">R16+S16</f>
         <v>0</v>
       </c>
-      <c r="R16" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="32" t="n">
+      <c r="R16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>58766</v>
@@ -5634,23 +6008,23 @@
       <c r="P17" s="21" t="n">
         <v>-0.0880441071367798</v>
       </c>
-      <c r="Q17" s="32" t="n">
+      <c r="Q17" s="22" t="n">
         <f aca="false">R17+S17</f>
         <v>1</v>
       </c>
-      <c r="R17" s="32" t="n">
+      <c r="R17" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="32" t="n">
+      <c r="S17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="28" t="n">
         <v>29383</v>
@@ -5693,23 +6067,23 @@
       <c r="P18" s="21" t="n">
         <v>-0.109246843412858</v>
       </c>
-      <c r="Q18" s="32" t="n">
+      <c r="Q18" s="22" t="n">
         <f aca="false">R18+S18</f>
         <v>0</v>
       </c>
-      <c r="R18" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="32" t="n">
+      <c r="R18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>25754</v>
@@ -5752,23 +6126,23 @@
       <c r="P19" s="21" t="n">
         <v>-0.479692474955347</v>
       </c>
-      <c r="Q19" s="32" t="n">
+      <c r="Q19" s="22" t="n">
         <f aca="false">R19+S19</f>
         <v>10</v>
       </c>
-      <c r="R19" s="32" t="n">
+      <c r="R19" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="S19" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="32" t="n">
+      <c r="S19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="28" t="n">
         <v>20767</v>
@@ -5811,23 +6185,23 @@
       <c r="P20" s="21" t="n">
         <v>-0.0610102566571965</v>
       </c>
-      <c r="Q20" s="32" t="n">
+      <c r="Q20" s="22" t="n">
         <f aca="false">R20+S20</f>
         <v>1</v>
       </c>
-      <c r="R20" s="32" t="n">
+      <c r="R20" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="S20" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="32" t="n">
+      <c r="S20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" s="28" t="n">
         <v>14692</v>
@@ -5870,23 +6244,23 @@
       <c r="P21" s="21" t="n">
         <v>-0.714130138851076</v>
       </c>
-      <c r="Q21" s="32" t="n">
+      <c r="Q21" s="22" t="n">
         <f aca="false">R21+S21</f>
         <v>4</v>
       </c>
-      <c r="R21" s="32" t="n">
+      <c r="R21" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="S21" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="32" t="n">
+      <c r="S21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" s="28" t="n">
         <v>11455</v>
@@ -5929,23 +6303,23 @@
       <c r="P22" s="21" t="n">
         <v>-0.75556525534701</v>
       </c>
-      <c r="Q22" s="32" t="n">
+      <c r="Q22" s="22" t="n">
         <f aca="false">R22+S22</f>
         <v>4</v>
       </c>
-      <c r="R22" s="32" t="n">
+      <c r="R22" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="S22" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="32" t="n">
+      <c r="S22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="28" t="n">
         <v>6615</v>
@@ -5988,23 +6362,23 @@
       <c r="P23" s="21" t="n">
         <v>0.647770219198791</v>
       </c>
-      <c r="Q23" s="32" t="n">
+      <c r="Q23" s="22" t="n">
         <f aca="false">R23+S23</f>
         <v>12</v>
       </c>
-      <c r="R23" s="32" t="n">
+      <c r="R23" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="S23" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="32" t="n">
+      <c r="S23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" s="28" t="n">
         <v>5715</v>
@@ -6047,23 +6421,23 @@
       <c r="P24" s="21" t="n">
         <v>-0.617322834645669</v>
       </c>
-      <c r="Q24" s="32" t="n">
+      <c r="Q24" s="22" t="n">
         <f aca="false">R24+S24</f>
         <v>35</v>
       </c>
-      <c r="R24" s="32" t="n">
+      <c r="R24" s="22" t="n">
         <v>35</v>
       </c>
-      <c r="S24" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="32" t="n">
+      <c r="S24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" s="28" t="n">
         <v>4572</v>
@@ -6106,23 +6480,23 @@
       <c r="P25" s="21" t="n">
         <v>-0.628171478565179</v>
       </c>
-      <c r="Q25" s="32" t="n">
+      <c r="Q25" s="22" t="n">
         <f aca="false">R25+S25</f>
         <v>13</v>
       </c>
-      <c r="R25" s="32" t="n">
+      <c r="R25" s="22" t="n">
         <v>13</v>
       </c>
-      <c r="S25" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="32" t="n">
+      <c r="S25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" s="28" t="n">
         <v>8868</v>
@@ -6165,23 +6539,23 @@
       <c r="P26" s="21" t="n">
         <v>-0.588971583220568</v>
       </c>
-      <c r="Q26" s="32" t="n">
+      <c r="Q26" s="22" t="n">
         <f aca="false">R26+S26</f>
         <v>15</v>
       </c>
-      <c r="R26" s="32" t="n">
+      <c r="R26" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="S26" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="32" t="n">
+      <c r="S26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" s="28" t="n">
         <v>7122</v>
@@ -6224,23 +6598,23 @@
       <c r="P27" s="21" t="n">
         <v>-0.0452120190957597</v>
       </c>
-      <c r="Q27" s="32" t="n">
+      <c r="Q27" s="22" t="n">
         <f aca="false">R27+S27</f>
         <v>0</v>
       </c>
-      <c r="R27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="32" t="n">
+      <c r="R27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" s="28" t="n">
         <v>3824</v>
@@ -6283,23 +6657,23 @@
       <c r="P28" s="21" t="n">
         <v>-0.364539748953975</v>
       </c>
-      <c r="Q28" s="32" t="n">
+      <c r="Q28" s="22" t="n">
         <f aca="false">R28+S28</f>
         <v>32</v>
       </c>
-      <c r="R28" s="32" t="n">
+      <c r="R28" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="S28" s="32" t="n">
+      <c r="S28" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="T28" s="32" t="n">
+      <c r="T28" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" s="28" t="n">
         <v>11904</v>
@@ -6342,23 +6716,23 @@
       <c r="P29" s="21" t="n">
         <v>-0.479166666666667</v>
       </c>
-      <c r="Q29" s="32" t="n">
+      <c r="Q29" s="22" t="n">
         <f aca="false">R29+S29</f>
         <v>6</v>
       </c>
-      <c r="R29" s="32" t="n">
+      <c r="R29" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="S29" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="32" t="n">
+      <c r="S29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" s="28" t="n">
         <v>4216</v>
@@ -6401,23 +6775,23 @@
       <c r="P30" s="21" t="n">
         <v>-0.743833017077799</v>
       </c>
-      <c r="Q30" s="32" t="n">
+      <c r="Q30" s="22" t="n">
         <f aca="false">R30+S30</f>
         <v>0</v>
       </c>
-      <c r="R30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="32" t="n">
+      <c r="R30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" s="28" t="n">
         <v>25684</v>
@@ -6460,23 +6834,23 @@
       <c r="P31" s="21" t="n">
         <v>-0.264133312568136</v>
       </c>
-      <c r="Q31" s="32" t="n">
+      <c r="Q31" s="22" t="n">
         <f aca="false">R31+S31</f>
         <v>3</v>
       </c>
-      <c r="R31" s="32" t="n">
+      <c r="R31" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="S31" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="32" t="n">
+      <c r="S31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B32" s="28" t="n">
         <v>5137</v>
@@ -6519,23 +6893,23 @@
       <c r="P32" s="21" t="n">
         <v>-0.828693790149893</v>
       </c>
-      <c r="Q32" s="32" t="n">
+      <c r="Q32" s="22" t="n">
         <f aca="false">R32+S32</f>
         <v>0</v>
       </c>
-      <c r="R32" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="32" t="n">
+      <c r="R32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B33" s="28" t="n">
         <v>25419</v>
@@ -6578,23 +6952,23 @@
       <c r="P33" s="21" t="n">
         <v>-0.713206656438097</v>
       </c>
-      <c r="Q33" s="32" t="n">
+      <c r="Q33" s="22" t="n">
         <f aca="false">R33+S33</f>
         <v>3</v>
       </c>
-      <c r="R33" s="32" t="n">
+      <c r="R33" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="S33" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="32" t="n">
+      <c r="S33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="28" t="n">
         <v>17696</v>
@@ -6637,23 +7011,23 @@
       <c r="P34" s="21" t="n">
         <v>-0.313404159132007</v>
       </c>
-      <c r="Q34" s="32" t="n">
+      <c r="Q34" s="22" t="n">
         <f aca="false">R34+S34</f>
         <v>0</v>
       </c>
-      <c r="R34" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="32" t="n">
+      <c r="R34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B35" s="28" t="n">
         <v>40957</v>
@@ -6696,23 +7070,23 @@
       <c r="P35" s="21" t="n">
         <v>-0.406694826281222</v>
       </c>
-      <c r="Q35" s="32" t="n">
+      <c r="Q35" s="22" t="n">
         <f aca="false">R35+S35</f>
         <v>0</v>
       </c>
-      <c r="R35" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="32" t="n">
+      <c r="R35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B36" s="28" t="n">
         <v>19364</v>
@@ -6755,23 +7129,23 @@
       <c r="P36" s="21" t="n">
         <v>-0.597190663086139</v>
       </c>
-      <c r="Q36" s="32" t="n">
+      <c r="Q36" s="22" t="n">
         <f aca="false">R36+S36</f>
         <v>1</v>
       </c>
-      <c r="R36" s="32" t="n">
+      <c r="R36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="S36" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="32" t="n">
+      <c r="S36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B37" s="28" t="n">
         <v>29043</v>
@@ -6814,23 +7188,23 @@
       <c r="P37" s="21" t="n">
         <v>-0.621251248149296</v>
       </c>
-      <c r="Q37" s="32" t="n">
+      <c r="Q37" s="22" t="n">
         <f aca="false">R37+S37</f>
         <v>0</v>
       </c>
-      <c r="R37" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="32" t="n">
+      <c r="R37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B38" s="28" t="n">
         <v>29102</v>
@@ -6873,23 +7247,23 @@
       <c r="P38" s="21" t="n">
         <v>1.06171397154835</v>
       </c>
-      <c r="Q38" s="32" t="n">
+      <c r="Q38" s="22" t="n">
         <f aca="false">R38+S38</f>
         <v>12</v>
       </c>
-      <c r="R38" s="32" t="n">
+      <c r="R38" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="S38" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="32" t="n">
+      <c r="S38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B39" s="28" t="n">
         <v>19364</v>
@@ -6932,23 +7306,23 @@
       <c r="P39" s="21" t="n">
         <v>-0.338979549679818</v>
       </c>
-      <c r="Q39" s="32" t="n">
+      <c r="Q39" s="22" t="n">
         <f aca="false">R39+S39</f>
         <v>0</v>
       </c>
-      <c r="R39" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="32" t="n">
+      <c r="R39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B40" s="28" t="n">
         <v>29043</v>
@@ -6991,23 +7365,23 @@
       <c r="P40" s="21" t="n">
         <v>-0.517956134008195</v>
       </c>
-      <c r="Q40" s="32" t="n">
+      <c r="Q40" s="22" t="n">
         <f aca="false">R40+S40</f>
         <v>0</v>
       </c>
-      <c r="R40" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="32" t="n">
+      <c r="R40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B41" s="28" t="n">
         <v>12093</v>
@@ -7050,23 +7424,23 @@
       <c r="P41" s="21" t="n">
         <v>-0.354998759612999</v>
       </c>
-      <c r="Q41" s="32" t="n">
+      <c r="Q41" s="22" t="n">
         <f aca="false">R41+S41</f>
         <v>4</v>
       </c>
-      <c r="R41" s="32" t="n">
+      <c r="R41" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="S41" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="32" t="n">
+      <c r="S41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B42" s="28" t="n">
         <v>5678</v>
@@ -7109,23 +7483,23 @@
       <c r="P42" s="21" t="n">
         <v>-0.144064811553364</v>
       </c>
-      <c r="Q42" s="32" t="n">
+      <c r="Q42" s="22" t="n">
         <f aca="false">R42+S42</f>
         <v>40</v>
       </c>
-      <c r="R42" s="32" t="n">
+      <c r="R42" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="S42" s="32" t="n">
+      <c r="S42" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="T42" s="32" t="n">
+      <c r="T42" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B43" s="28" t="n">
         <v>13020</v>
@@ -7168,23 +7542,23 @@
       <c r="P43" s="21" t="n">
         <v>-0.585253456221198</v>
       </c>
-      <c r="Q43" s="32" t="n">
+      <c r="Q43" s="22" t="n">
         <f aca="false">R43+S43</f>
         <v>0</v>
       </c>
-      <c r="R43" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="32" t="n">
+      <c r="R43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B44" s="28" t="n">
         <v>117535</v>
@@ -7227,23 +7601,23 @@
       <c r="P44" s="21" t="n">
         <v>-0.446973242013017</v>
       </c>
-      <c r="Q44" s="32" t="n">
+      <c r="Q44" s="22" t="n">
         <f aca="false">R44+S44</f>
         <v>1</v>
       </c>
-      <c r="R44" s="32" t="n">
+      <c r="R44" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="S44" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="32" t="n">
+      <c r="S44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B45" s="28" t="n">
         <v>22729</v>
@@ -7286,23 +7660,23 @@
       <c r="P45" s="21" t="n">
         <v>-0.208060187425756</v>
       </c>
-      <c r="Q45" s="32" t="n">
+      <c r="Q45" s="22" t="n">
         <f aca="false">R45+S45</f>
         <v>5</v>
       </c>
-      <c r="R45" s="32" t="n">
+      <c r="R45" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="S45" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="32" t="n">
+      <c r="S45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B46" s="28" t="n">
         <v>27699</v>
@@ -7345,23 +7719,23 @@
       <c r="P46" s="21" t="n">
         <v>-0.205747499909744</v>
       </c>
-      <c r="Q46" s="32" t="n">
+      <c r="Q46" s="22" t="n">
         <f aca="false">R46+S46</f>
         <v>0</v>
       </c>
-      <c r="R46" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="32" t="n">
+      <c r="R46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B47" s="28" t="n">
         <v>2598</v>
@@ -7404,23 +7778,23 @@
       <c r="P47" s="21" t="n">
         <v>-0.30715935334873</v>
       </c>
-      <c r="Q47" s="32" t="n">
+      <c r="Q47" s="22" t="n">
         <f aca="false">R47+S47</f>
         <v>0</v>
       </c>
-      <c r="R47" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="32" t="n">
+      <c r="R47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B48" s="28" t="n">
         <v>18296</v>
@@ -7463,23 +7837,23 @@
       <c r="P48" s="21" t="n">
         <v>-0.196545693047661</v>
       </c>
-      <c r="Q48" s="32" t="n">
+      <c r="Q48" s="22" t="n">
         <f aca="false">R48+S48</f>
         <v>0</v>
       </c>
-      <c r="R48" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="32" t="n">
+      <c r="R48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B49" s="28" t="n">
         <v>7858</v>
@@ -7522,23 +7896,23 @@
       <c r="P49" s="21" t="n">
         <v>0.11987783150929</v>
       </c>
-      <c r="Q49" s="32" t="n">
+      <c r="Q49" s="22" t="n">
         <f aca="false">R49+S49</f>
         <v>6</v>
       </c>
-      <c r="R49" s="32" t="n">
+      <c r="R49" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="S49" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="32" t="n">
+      <c r="S49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B50" s="28" t="n">
         <v>7030</v>
@@ -7581,23 +7955,23 @@
       <c r="P50" s="21" t="n">
         <v>-0.516358463726885</v>
       </c>
-      <c r="Q50" s="32" t="n">
+      <c r="Q50" s="22" t="n">
         <f aca="false">R50+S50</f>
         <v>3</v>
       </c>
-      <c r="R50" s="32" t="n">
+      <c r="R50" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="S50" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="32" t="n">
+      <c r="S50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B51" s="28" t="n">
         <v>1556</v>
@@ -7640,23 +8014,23 @@
       <c r="P51" s="21" t="n">
         <v>-0.663714652956298</v>
       </c>
-      <c r="Q51" s="32" t="n">
+      <c r="Q51" s="22" t="n">
         <f aca="false">R51+S51</f>
         <v>0</v>
       </c>
-      <c r="R51" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="32" t="n">
+      <c r="R51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B52" s="28" t="n">
         <v>1040</v>
@@ -7699,23 +8073,23 @@
       <c r="P52" s="21" t="n">
         <v>-0.652644230769231</v>
       </c>
-      <c r="Q52" s="32" t="n">
+      <c r="Q52" s="22" t="n">
         <f aca="false">R52+S52</f>
         <v>0</v>
       </c>
-      <c r="R52" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="32" t="n">
+      <c r="R52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B53" s="28" t="n">
         <v>727</v>
@@ -7758,23 +8132,23 @@
       <c r="P53" s="21" t="n">
         <v>-0.722943603851444</v>
       </c>
-      <c r="Q53" s="32" t="n">
+      <c r="Q53" s="22" t="n">
         <f aca="false">R53+S53</f>
         <v>0</v>
       </c>
-      <c r="R53" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="32" t="n">
+      <c r="R53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B54" s="28" t="n">
         <v>779</v>
@@ -7817,23 +8191,23 @@
       <c r="P54" s="21" t="n">
         <v>-0.165596919127086</v>
       </c>
-      <c r="Q54" s="32" t="n">
+      <c r="Q54" s="22" t="n">
         <f aca="false">R54+S54</f>
         <v>0</v>
       </c>
-      <c r="R54" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="32" t="n">
+      <c r="R54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B55" s="28" t="n">
         <v>29000</v>
@@ -7876,44 +8250,44 @@
       <c r="P55" s="16" t="n">
         <v>99837</v>
       </c>
-      <c r="Q55" s="32" t="n">
+      <c r="Q55" s="22" t="n">
         <f aca="false">R55+S55</f>
         <v>12</v>
       </c>
-      <c r="R55" s="32" t="n">
+      <c r="R55" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="S55" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="32" t="n">
+      <c r="S55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B56" s="34" t="n">
+        <v>89</v>
+      </c>
+      <c r="B56" s="33" t="n">
         <v>1086326</v>
       </c>
-      <c r="C56" s="34" t="n">
+      <c r="C56" s="33" t="n">
         <v>316697.2</v>
       </c>
-      <c r="D56" s="34" t="n">
+      <c r="D56" s="33" t="n">
         <v>402454.15</v>
       </c>
-      <c r="E56" s="34" t="n">
+      <c r="E56" s="33" t="n">
         <v>657081</v>
       </c>
-      <c r="F56" s="34" t="n">
+      <c r="F56" s="33" t="n">
         <v>673500</v>
       </c>
-      <c r="G56" s="34" t="n">
+      <c r="G56" s="33" t="n">
         <v>733394.6</v>
       </c>
-      <c r="H56" s="34"/>
-      <c r="I56" s="35" t="n">
+      <c r="H56" s="33"/>
+      <c r="I56" s="34" t="n">
         <v>221858.15</v>
       </c>
       <c r="J56" s="27"/>
@@ -7963,7 +8337,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R56"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42.14"/>
@@ -7974,11 +8348,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="3.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="12" style="1" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="51" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -8029,31 +8404,37 @@
       <c r="R1" s="11" t="s">
         <v>32</v>
       </c>
+      <c r="S1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="37" t="n">
+      <c r="A2" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="36" t="n">
         <v>4364</v>
       </c>
-      <c r="C2" s="37" t="n">
+      <c r="C2" s="36" t="n">
         <v>1288</v>
       </c>
-      <c r="D2" s="37" t="n">
+      <c r="D2" s="36" t="n">
         <v>1619.1</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="36" t="n">
         <v>2837</v>
       </c>
-      <c r="F2" s="37" t="n">
+      <c r="F2" s="36" t="n">
         <v>3500</v>
       </c>
-      <c r="G2" s="37" t="n">
+      <c r="G2" s="36" t="n">
         <v>2462</v>
       </c>
-      <c r="H2" s="38"/>
-      <c r="I2" s="39" t="n">
+      <c r="H2" s="37"/>
+      <c r="I2" s="38" t="n">
         <f aca="false">MIN(E2:G2)</f>
         <v>2462</v>
       </c>
@@ -8082,37 +8463,44 @@
         <f aca="false">G2/$B2-1</f>
         <v>-0.435838680109991</v>
       </c>
-      <c r="Q2" s="40" t="n">
+      <c r="Q2" s="22" t="n">
+        <f aca="false">R2+S2</f>
+        <v>511</v>
+      </c>
+      <c r="R2" s="22" t="n">
         <v>120</v>
       </c>
-      <c r="R2" s="40" t="n">
+      <c r="S2" s="22" t="n">
+        <v>391</v>
+      </c>
+      <c r="T2" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="37" t="n">
+      <c r="A3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="36" t="n">
         <v>5866</v>
       </c>
-      <c r="C3" s="37" t="n">
+      <c r="C3" s="36" t="n">
         <v>3312</v>
       </c>
-      <c r="D3" s="37" t="n">
+      <c r="D3" s="36" t="n">
         <v>2176.3</v>
       </c>
-      <c r="E3" s="37" t="n">
+      <c r="E3" s="36" t="n">
         <v>3813</v>
       </c>
-      <c r="F3" s="37" t="n">
+      <c r="F3" s="36" t="n">
         <v>4500</v>
       </c>
-      <c r="G3" s="37" t="n">
+      <c r="G3" s="36" t="n">
         <v>3162</v>
       </c>
-      <c r="H3" s="38"/>
-      <c r="I3" s="39" t="n">
+      <c r="H3" s="37"/>
+      <c r="I3" s="38" t="n">
         <f aca="false">MIN(E3:G3)</f>
         <v>3162</v>
       </c>
@@ -8141,37 +8529,44 @@
         <f aca="false">G3/$B3-1</f>
         <v>-0.460961472894647</v>
       </c>
-      <c r="Q3" s="40" t="n">
+      <c r="Q3" s="22" t="n">
+        <f aca="false">R3+S3</f>
         <v>56</v>
       </c>
-      <c r="R3" s="40" t="n">
+      <c r="R3" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="S3" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="37" t="n">
+      <c r="A4" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="36" t="n">
         <v>8729</v>
       </c>
-      <c r="C4" s="37" t="n">
+      <c r="C4" s="36" t="n">
         <v>4968</v>
       </c>
-      <c r="D4" s="37" t="n">
+      <c r="D4" s="36" t="n">
         <v>2590.7</v>
       </c>
-      <c r="E4" s="37" t="n">
+      <c r="E4" s="36" t="n">
         <v>5674</v>
       </c>
-      <c r="F4" s="37" t="n">
+      <c r="F4" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="G4" s="37" t="n">
+      <c r="G4" s="36" t="n">
         <v>5400</v>
       </c>
-      <c r="H4" s="38"/>
-      <c r="I4" s="39" t="n">
+      <c r="H4" s="37"/>
+      <c r="I4" s="38" t="n">
         <f aca="false">MIN(E4:G4)</f>
         <v>5400</v>
       </c>
@@ -8200,37 +8595,44 @@
         <f aca="false">G4/$B4-1</f>
         <v>-0.381372436705235</v>
       </c>
-      <c r="Q4" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="40" t="n">
+      <c r="Q4" s="22" t="n">
+        <f aca="false">R4+S4</f>
+        <v>0</v>
+      </c>
+      <c r="R4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="37" t="n">
+      <c r="A5" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="36" t="n">
         <v>4364</v>
       </c>
-      <c r="C5" s="37" t="n">
+      <c r="C5" s="36" t="n">
         <v>1288</v>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="36" t="n">
         <v>1619.1</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="36" t="n">
         <v>2837</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="36" t="n">
         <v>3500</v>
       </c>
-      <c r="G5" s="37" t="n">
+      <c r="G5" s="36" t="n">
         <v>1900</v>
       </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39" t="n">
+      <c r="H5" s="37"/>
+      <c r="I5" s="38" t="n">
         <f aca="false">MIN(E5:G5)</f>
         <v>1900</v>
       </c>
@@ -8259,37 +8661,44 @@
         <f aca="false">G5/$B5-1</f>
         <v>-0.564619615032081</v>
       </c>
-      <c r="Q5" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="40" t="n">
+      <c r="Q5" s="22" t="n">
+        <f aca="false">R5+S5</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="37" t="n">
+      <c r="A6" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="36" t="n">
         <v>6546</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="36" t="n">
         <v>2392</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="36" t="n">
         <v>2428.65</v>
       </c>
-      <c r="E6" s="37" t="n">
+      <c r="E6" s="36" t="n">
         <v>4255</v>
       </c>
-      <c r="F6" s="37" t="n">
+      <c r="F6" s="36" t="n">
         <v>4000</v>
       </c>
-      <c r="G6" s="37" t="n">
+      <c r="G6" s="36" t="n">
         <v>4540</v>
       </c>
-      <c r="H6" s="38"/>
-      <c r="I6" s="39" t="n">
+      <c r="H6" s="37"/>
+      <c r="I6" s="38" t="n">
         <f aca="false">MIN(E6:G6)</f>
         <v>4000</v>
       </c>
@@ -8318,37 +8727,44 @@
         <f aca="false">G6/$B6-1</f>
         <v>-0.306446684998472</v>
       </c>
-      <c r="Q6" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="40" t="n">
+      <c r="Q6" s="22" t="n">
+        <f aca="false">R6+S6</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="37" t="n">
+      <c r="A7" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="36" t="n">
         <v>844</v>
       </c>
-      <c r="C7" s="37" t="n">
+      <c r="C7" s="36" t="n">
         <v>552</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="36" t="n">
         <v>2920.05</v>
       </c>
-      <c r="E7" s="37" t="n">
+      <c r="E7" s="36" t="n">
         <v>549</v>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="36" t="n">
         <v>4000</v>
       </c>
-      <c r="G7" s="37" t="n">
+      <c r="G7" s="36" t="n">
         <v>562.67</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39" t="n">
+      <c r="H7" s="37"/>
+      <c r="I7" s="38" t="n">
         <f aca="false">MIN(E7:G7)</f>
         <v>549</v>
       </c>
@@ -8377,35 +8793,42 @@
         <f aca="false">G7/$B7-1</f>
         <v>-0.333329383886256</v>
       </c>
-      <c r="Q7" s="40" t="n">
+      <c r="Q7" s="22" t="n">
+        <f aca="false">R7+S7</f>
+        <v>579</v>
+      </c>
+      <c r="R7" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="R7" s="40" t="n">
+      <c r="S7" s="22" t="n">
+        <v>576</v>
+      </c>
+      <c r="T7" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="37" t="n">
+      <c r="A8" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="36" t="n">
         <v>7946</v>
       </c>
-      <c r="C8" s="37" t="n">
+      <c r="C8" s="36" t="n">
         <v>2208</v>
       </c>
-      <c r="D8" s="37" t="n">
+      <c r="D8" s="36" t="n">
         <v>2948.05</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E8" s="36" t="n">
         <v>5165</v>
       </c>
-      <c r="F8" s="37" t="n">
+      <c r="F8" s="36" t="n">
         <v>6000</v>
       </c>
-      <c r="G8" s="41"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39" t="n">
+      <c r="G8" s="39"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38" t="n">
         <f aca="false">MIN(E8:G8)</f>
         <v>5165</v>
       </c>
@@ -8434,37 +8857,44 @@
         <f aca="false">G8/$B8-1</f>
         <v>-1</v>
       </c>
-      <c r="Q8" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="40" t="n">
+      <c r="Q8" s="22" t="n">
+        <f aca="false">R8+S8</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="37" t="n">
+      <c r="A9" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="36" t="n">
         <v>13554</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="36" t="n">
         <v>4968</v>
       </c>
-      <c r="D9" s="37" t="n">
+      <c r="D9" s="36" t="n">
         <v>5028.45</v>
       </c>
-      <c r="E9" s="37" t="n">
+      <c r="E9" s="36" t="n">
         <v>8810</v>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F9" s="36" t="n">
         <v>11000</v>
       </c>
-      <c r="G9" s="37" t="n">
+      <c r="G9" s="36" t="n">
         <v>8800</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="39" t="n">
+      <c r="H9" s="37"/>
+      <c r="I9" s="38" t="n">
         <f aca="false">MIN(E9:G9)</f>
         <v>8800</v>
       </c>
@@ -8493,37 +8923,44 @@
         <f aca="false">G9/$B9-1</f>
         <v>-0.350745167478235</v>
       </c>
-      <c r="Q9" s="40" t="n">
+      <c r="Q9" s="22" t="n">
+        <f aca="false">R9+S9</f>
         <v>17</v>
       </c>
-      <c r="R9" s="40" t="n">
+      <c r="R9" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="S9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="37" t="n">
+      <c r="A10" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="36" t="n">
         <v>27108</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="36" t="n">
         <v>1840</v>
       </c>
-      <c r="D10" s="37" t="n">
+      <c r="D10" s="36" t="n">
         <v>10056.9</v>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="36" t="n">
         <v>17620</v>
       </c>
-      <c r="F10" s="37" t="n">
+      <c r="F10" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="G10" s="37" t="n">
+      <c r="G10" s="36" t="n">
         <v>25800</v>
       </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="39" t="n">
+      <c r="H10" s="37"/>
+      <c r="I10" s="38" t="n">
         <f aca="false">MIN(E10:G10)</f>
         <v>17620</v>
       </c>
@@ -8552,37 +8989,44 @@
         <f aca="false">G10/$B10-1</f>
         <v>-0.0482514386896857</v>
       </c>
-      <c r="Q10" s="40" t="n">
+      <c r="Q10" s="22" t="n">
+        <f aca="false">R10+S10</f>
         <v>5</v>
       </c>
-      <c r="R10" s="40" t="n">
+      <c r="R10" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="37" t="n">
+      <c r="A11" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="36" t="n">
         <v>14545</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="36" t="n">
         <v>1104</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="36" t="n">
         <v>5396.3</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="36" t="n">
         <v>9454</v>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="36" t="n">
         <v>9000</v>
       </c>
-      <c r="G11" s="37" t="n">
+      <c r="G11" s="36" t="n">
         <v>12000</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39" t="n">
+      <c r="H11" s="37"/>
+      <c r="I11" s="38" t="n">
         <f aca="false">MIN(E11:G11)</f>
         <v>9000</v>
       </c>
@@ -8611,37 +9055,44 @@
         <f aca="false">G11/$B11-1</f>
         <v>-0.174974217944311</v>
       </c>
-      <c r="Q11" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="40" t="n">
+      <c r="Q11" s="22" t="n">
+        <f aca="false">R11+S11</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="37" t="n">
+      <c r="A12" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="36" t="n">
         <v>11785</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="36" t="n">
         <v>736</v>
       </c>
-      <c r="D12" s="37" t="n">
+      <c r="D12" s="36" t="n">
         <v>4372.2</v>
       </c>
-      <c r="E12" s="37" t="n">
+      <c r="E12" s="36" t="n">
         <v>7660</v>
       </c>
-      <c r="F12" s="37" t="n">
+      <c r="F12" s="36" t="n">
         <v>8000</v>
       </c>
-      <c r="G12" s="37" t="n">
+      <c r="G12" s="36" t="n">
         <v>7890</v>
       </c>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39" t="n">
+      <c r="H12" s="37"/>
+      <c r="I12" s="38" t="n">
         <f aca="false">MIN(E12:G12)</f>
         <v>7660</v>
       </c>
@@ -8670,37 +9121,44 @@
         <f aca="false">G12/$B12-1</f>
         <v>-0.330504879083581</v>
       </c>
-      <c r="Q12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="40" t="n">
+      <c r="Q12" s="22" t="n">
+        <f aca="false">R12+S12</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" s="37" t="n">
+      <c r="A13" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="36" t="n">
         <v>117535</v>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C13" s="36" t="n">
         <v>35000</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="36" t="n">
         <v>10901.45</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="36" t="n">
         <v>19100</v>
       </c>
-      <c r="F13" s="37" t="n">
+      <c r="F13" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="G13" s="37" t="n">
+      <c r="G13" s="36" t="n">
         <v>25000</v>
       </c>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39" t="n">
+      <c r="H13" s="37"/>
+      <c r="I13" s="38" t="n">
         <f aca="false">MIN(E13:G13)</f>
         <v>18000</v>
       </c>
@@ -8729,37 +9187,44 @@
         <f aca="false">G13/$B13-1</f>
         <v>-0.787297400774238</v>
       </c>
-      <c r="Q13" s="40" t="n">
+      <c r="Q13" s="22" t="n">
+        <f aca="false">R13+S13</f>
         <v>1</v>
       </c>
-      <c r="R13" s="40" t="n">
+      <c r="R13" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="37" t="n">
+      <c r="A14" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="36" t="n">
         <v>58768</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="36" t="n">
         <v>4416</v>
       </c>
-      <c r="D14" s="37" t="n">
+      <c r="D14" s="36" t="n">
         <v>5450.55</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="36" t="n">
         <v>9550</v>
       </c>
-      <c r="F14" s="37" t="n">
+      <c r="F14" s="36" t="n">
         <v>10000</v>
       </c>
-      <c r="G14" s="37" t="n">
+      <c r="G14" s="36" t="n">
         <v>12800</v>
       </c>
-      <c r="H14" s="38"/>
-      <c r="I14" s="39" t="n">
+      <c r="H14" s="37"/>
+      <c r="I14" s="38" t="n">
         <f aca="false">MIN(E14:G14)</f>
         <v>9550</v>
       </c>
@@ -8788,37 +9253,44 @@
         <f aca="false">G14/$B14-1</f>
         <v>-0.782194391505581</v>
       </c>
-      <c r="Q14" s="40" t="n">
+      <c r="Q14" s="22" t="n">
+        <f aca="false">R14+S14</f>
         <v>8</v>
       </c>
-      <c r="R14" s="40" t="n">
+      <c r="R14" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="37" t="n">
+      <c r="A15" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="36" t="n">
         <v>41136</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="36" t="n">
         <v>15000</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="36" t="n">
         <v>3816.05</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="36" t="n">
         <v>6686</v>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F15" s="36" t="n">
         <v>8000</v>
       </c>
-      <c r="G15" s="37" t="n">
+      <c r="G15" s="36" t="n">
         <v>8760</v>
       </c>
-      <c r="H15" s="38"/>
-      <c r="I15" s="39" t="n">
+      <c r="H15" s="37"/>
+      <c r="I15" s="38" t="n">
         <f aca="false">MIN(E15:G15)</f>
         <v>6686</v>
       </c>
@@ -8847,37 +9319,44 @@
         <f aca="false">G15/$B15-1</f>
         <v>-0.787047841306884</v>
       </c>
-      <c r="Q15" s="40" t="n">
+      <c r="Q15" s="22" t="n">
+        <f aca="false">R15+S15</f>
         <v>17</v>
       </c>
-      <c r="R15" s="40" t="n">
+      <c r="R15" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="S15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="37" t="n">
+      <c r="A16" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="36" t="n">
         <v>41136</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D16" s="37" t="n">
+      <c r="D16" s="36" t="n">
         <v>15261.75</v>
       </c>
-      <c r="E16" s="37" t="n">
+      <c r="E16" s="36" t="n">
         <v>26738</v>
       </c>
-      <c r="F16" s="37" t="n">
+      <c r="F16" s="36" t="n">
         <v>28000</v>
       </c>
-      <c r="G16" s="37" t="n">
+      <c r="G16" s="36" t="n">
         <v>37258</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="39" t="n">
+      <c r="H16" s="37"/>
+      <c r="I16" s="38" t="n">
         <f aca="false">MIN(E16:G16)</f>
         <v>26738</v>
       </c>
@@ -8906,37 +9385,44 @@
         <f aca="false">G16/$B16-1</f>
         <v>-0.0942726565538701</v>
       </c>
-      <c r="Q16" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="40" t="n">
+      <c r="Q16" s="22" t="n">
+        <f aca="false">R16+S16</f>
+        <v>0</v>
+      </c>
+      <c r="R16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="37" t="n">
+      <c r="A17" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="36" t="n">
         <v>58766</v>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C17" s="36" t="n">
         <v>6500</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="36" t="n">
         <v>21802.2</v>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="36" t="n">
         <v>38198</v>
       </c>
-      <c r="F17" s="37" t="n">
+      <c r="F17" s="36" t="n">
         <v>35000</v>
       </c>
-      <c r="G17" s="37" t="n">
+      <c r="G17" s="36" t="n">
         <v>53592</v>
       </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39" t="n">
+      <c r="H17" s="37"/>
+      <c r="I17" s="38" t="n">
         <f aca="false">MIN(E17:G17)</f>
         <v>35000</v>
       </c>
@@ -8965,37 +9451,44 @@
         <f aca="false">G17/$B17-1</f>
         <v>-0.0880441071367798</v>
       </c>
-      <c r="Q17" s="40" t="n">
+      <c r="Q17" s="22" t="n">
+        <f aca="false">R17+S17</f>
         <v>1</v>
       </c>
-      <c r="R17" s="40" t="n">
+      <c r="R17" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="37" t="n">
+      <c r="A18" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="36" t="n">
         <v>29383</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="36" t="n">
         <v>2500</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="36" t="n">
         <v>10901.45</v>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="36" t="n">
         <v>19099</v>
       </c>
-      <c r="F18" s="37" t="n">
+      <c r="F18" s="36" t="n">
         <v>7000</v>
       </c>
-      <c r="G18" s="37" t="n">
+      <c r="G18" s="36" t="n">
         <v>26173</v>
       </c>
-      <c r="H18" s="38"/>
-      <c r="I18" s="39" t="n">
+      <c r="H18" s="37"/>
+      <c r="I18" s="38" t="n">
         <f aca="false">MIN(E18:G18)</f>
         <v>7000</v>
       </c>
@@ -9024,37 +9517,44 @@
         <f aca="false">G18/$B18-1</f>
         <v>-0.109246843412858</v>
       </c>
-      <c r="Q18" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="40" t="n">
+      <c r="Q18" s="22" t="n">
+        <f aca="false">R18+S18</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="37" t="n">
+      <c r="A19" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="36" t="n">
         <v>25754</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="36" t="n">
         <v>4416</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="36" t="n">
         <v>1359.4</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="36" t="n">
         <v>16740</v>
       </c>
-      <c r="F19" s="37" t="n">
+      <c r="F19" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="G19" s="37" t="n">
+      <c r="G19" s="36" t="n">
         <v>13400</v>
       </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39" t="n">
+      <c r="H19" s="37"/>
+      <c r="I19" s="38" t="n">
         <f aca="false">MIN(E19:G19)</f>
         <v>13400</v>
       </c>
@@ -9083,37 +9583,44 @@
         <f aca="false">G19/$B19-1</f>
         <v>-0.479692474955347</v>
       </c>
-      <c r="Q19" s="40" t="n">
+      <c r="Q19" s="22" t="n">
+        <f aca="false">R19+S19</f>
         <v>10</v>
       </c>
-      <c r="R19" s="40" t="n">
+      <c r="R19" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="S19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="37" t="n">
+      <c r="A20" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="36" t="n">
         <v>20767</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="36" t="n">
         <v>367</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="36" t="n">
         <v>7704.55</v>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="36" t="n">
         <v>13499</v>
       </c>
-      <c r="F20" s="37" t="n">
+      <c r="F20" s="36" t="n">
         <v>15000</v>
       </c>
-      <c r="G20" s="37" t="n">
+      <c r="G20" s="36" t="n">
         <v>19500</v>
       </c>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39" t="n">
+      <c r="H20" s="37"/>
+      <c r="I20" s="38" t="n">
         <f aca="false">MIN(E20:G20)</f>
         <v>13499</v>
       </c>
@@ -9142,37 +9649,44 @@
         <f aca="false">G20/$B20-1</f>
         <v>-0.0610102566571965</v>
       </c>
-      <c r="Q20" s="40" t="n">
+      <c r="Q20" s="22" t="n">
+        <f aca="false">R20+S20</f>
         <v>1</v>
       </c>
-      <c r="R20" s="40" t="n">
+      <c r="R20" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="37" t="n">
+      <c r="A21" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="36" t="n">
         <v>14692</v>
       </c>
-      <c r="C21" s="37" t="n">
+      <c r="C21" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="36" t="n">
         <v>5450.55</v>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="36" t="n">
         <v>9550</v>
       </c>
-      <c r="F21" s="37" t="n">
+      <c r="F21" s="36" t="n">
         <v>11000</v>
       </c>
-      <c r="G21" s="37" t="n">
+      <c r="G21" s="36" t="n">
         <v>4200</v>
       </c>
-      <c r="H21" s="38"/>
-      <c r="I21" s="39" t="n">
+      <c r="H21" s="37"/>
+      <c r="I21" s="38" t="n">
         <f aca="false">MIN(E21:G21)</f>
         <v>4200</v>
       </c>
@@ -9201,37 +9715,44 @@
         <f aca="false">G21/$B21-1</f>
         <v>-0.714130138851076</v>
       </c>
-      <c r="Q21" s="40" t="n">
+      <c r="Q21" s="22" t="n">
+        <f aca="false">R21+S21</f>
         <v>4</v>
       </c>
-      <c r="R21" s="40" t="n">
+      <c r="R21" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="37" t="n">
+      <c r="A22" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="36" t="n">
         <v>11455</v>
       </c>
-      <c r="C22" s="37" t="n">
+      <c r="C22" s="36" t="n">
         <v>4048</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="36" t="n">
         <v>4250.05</v>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="36" t="n">
         <v>7446</v>
       </c>
-      <c r="F22" s="37" t="n">
+      <c r="F22" s="36" t="n">
         <v>8000</v>
       </c>
-      <c r="G22" s="37" t="n">
+      <c r="G22" s="36" t="n">
         <v>2800</v>
       </c>
-      <c r="H22" s="38"/>
-      <c r="I22" s="39" t="n">
+      <c r="H22" s="37"/>
+      <c r="I22" s="38" t="n">
         <f aca="false">MIN(E22:G22)</f>
         <v>2800</v>
       </c>
@@ -9260,37 +9781,44 @@
         <f aca="false">G22/$B22-1</f>
         <v>-0.75556525534701</v>
       </c>
-      <c r="Q22" s="40" t="n">
+      <c r="Q22" s="22" t="n">
+        <f aca="false">R22+S22</f>
         <v>4</v>
       </c>
-      <c r="R22" s="40" t="n">
+      <c r="R22" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="36" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="37" t="n">
+      <c r="A23" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="36" t="n">
         <v>6615</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C23" s="36" t="n">
         <v>4500</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D23" s="36" t="n">
         <v>2454.2</v>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="36" t="n">
         <v>4300</v>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F23" s="36" t="n">
         <v>5000</v>
       </c>
-      <c r="G23" s="37" t="n">
+      <c r="G23" s="36" t="n">
         <v>10900</v>
       </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39" t="n">
+      <c r="H23" s="37"/>
+      <c r="I23" s="38" t="n">
         <f aca="false">MIN(E23:G23)</f>
         <v>4300</v>
       </c>
@@ -9319,37 +9847,44 @@
         <f aca="false">G23/$B23-1</f>
         <v>0.647770219198791</v>
       </c>
-      <c r="Q23" s="40" t="n">
+      <c r="Q23" s="22" t="n">
+        <f aca="false">R23+S23</f>
         <v>12</v>
       </c>
-      <c r="R23" s="40" t="n">
+      <c r="R23" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" s="37" t="n">
+      <c r="A24" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="36" t="n">
         <v>5715</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="36" t="n">
         <v>1104</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="36" t="n">
         <v>2120.3</v>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="36" t="n">
         <v>3715</v>
       </c>
-      <c r="F24" s="37" t="n">
+      <c r="F24" s="36" t="n">
         <v>4000</v>
       </c>
-      <c r="G24" s="37" t="n">
+      <c r="G24" s="36" t="n">
         <v>2187</v>
       </c>
-      <c r="H24" s="38"/>
-      <c r="I24" s="39" t="n">
+      <c r="H24" s="37"/>
+      <c r="I24" s="38" t="n">
         <f aca="false">MIN(E24:G24)</f>
         <v>2187</v>
       </c>
@@ -9378,37 +9913,44 @@
         <f aca="false">G24/$B24-1</f>
         <v>-0.617322834645669</v>
       </c>
-      <c r="Q24" s="40" t="n">
+      <c r="Q24" s="22" t="n">
+        <f aca="false">R24+S24</f>
         <v>35</v>
       </c>
-      <c r="R24" s="40" t="n">
+      <c r="R24" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="S24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="B25" s="37" t="n">
+      <c r="A25" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="36" t="n">
         <v>4572</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="36" t="n">
         <v>1656</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="36" t="n">
         <v>1696.1</v>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="36" t="n">
         <v>2972</v>
       </c>
-      <c r="F25" s="37" t="n">
+      <c r="F25" s="36" t="n">
         <v>3500</v>
       </c>
-      <c r="G25" s="37" t="n">
+      <c r="G25" s="36" t="n">
         <v>1700</v>
       </c>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39" t="n">
+      <c r="H25" s="37"/>
+      <c r="I25" s="38" t="n">
         <f aca="false">MIN(E25:G25)</f>
         <v>1700</v>
       </c>
@@ -9437,37 +9979,44 @@
         <f aca="false">G25/$B25-1</f>
         <v>-0.628171478565179</v>
       </c>
-      <c r="Q25" s="40" t="n">
+      <c r="Q25" s="22" t="n">
+        <f aca="false">R25+S25</f>
         <v>13</v>
       </c>
-      <c r="R25" s="40" t="n">
+      <c r="R25" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="S25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="37" t="n">
+      <c r="A26" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="36" t="n">
         <v>8868</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="36" t="n">
         <v>3496</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="36" t="n">
         <v>3290</v>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E26" s="36" t="n">
         <v>5764</v>
       </c>
-      <c r="F26" s="37" t="n">
+      <c r="F26" s="36" t="n">
         <v>7000</v>
       </c>
-      <c r="G26" s="37" t="n">
+      <c r="G26" s="36" t="n">
         <v>3645</v>
       </c>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39" t="n">
+      <c r="H26" s="37"/>
+      <c r="I26" s="38" t="n">
         <f aca="false">MIN(E26:G26)</f>
         <v>3645</v>
       </c>
@@ -9496,37 +10045,44 @@
         <f aca="false">G26/$B26-1</f>
         <v>-0.588971583220568</v>
       </c>
-      <c r="Q26" s="40" t="n">
+      <c r="Q26" s="22" t="n">
+        <f aca="false">R26+S26</f>
         <v>15</v>
       </c>
-      <c r="R26" s="40" t="n">
+      <c r="R26" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="S26" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B27" s="37" t="n">
+      <c r="A27" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="36" t="n">
         <v>7122</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="36" t="n">
         <v>1840</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="36" t="n">
         <v>2642.15</v>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="36" t="n">
         <v>4629</v>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F27" s="36" t="n">
         <v>5000</v>
       </c>
-      <c r="G27" s="37" t="n">
+      <c r="G27" s="36" t="n">
         <v>6800</v>
       </c>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39" t="n">
+      <c r="H27" s="37"/>
+      <c r="I27" s="38" t="n">
         <f aca="false">MIN(E27:G27)</f>
         <v>4629</v>
       </c>
@@ -9555,37 +10111,44 @@
         <f aca="false">G27/$B27-1</f>
         <v>-0.0452120190957597</v>
       </c>
-      <c r="Q27" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="40" t="n">
+      <c r="Q27" s="22" t="n">
+        <f aca="false">R27+S27</f>
+        <v>0</v>
+      </c>
+      <c r="R27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="37" t="n">
+      <c r="A28" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="36" t="n">
         <v>3824</v>
       </c>
-      <c r="C28" s="37" t="n">
+      <c r="C28" s="36" t="n">
         <v>1104</v>
       </c>
-      <c r="D28" s="37" t="n">
+      <c r="D28" s="36" t="n">
         <v>1418.9</v>
       </c>
-      <c r="E28" s="37" t="n">
+      <c r="E28" s="36" t="n">
         <v>2486</v>
       </c>
-      <c r="F28" s="37" t="n">
+      <c r="F28" s="36" t="n">
         <v>2500</v>
       </c>
-      <c r="G28" s="37" t="n">
+      <c r="G28" s="36" t="n">
         <v>2430</v>
       </c>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39" t="n">
+      <c r="H28" s="37"/>
+      <c r="I28" s="38" t="n">
         <f aca="false">MIN(E28:G28)</f>
         <v>2430</v>
       </c>
@@ -9614,37 +10177,44 @@
         <f aca="false">G28/$B28-1</f>
         <v>-0.364539748953975</v>
       </c>
-      <c r="Q28" s="40" t="n">
+      <c r="Q28" s="22" t="n">
+        <f aca="false">R28+S28</f>
+        <v>32</v>
+      </c>
+      <c r="R28" s="22" t="n">
         <v>11</v>
       </c>
-      <c r="R28" s="40" t="n">
+      <c r="S28" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="T28" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="37" t="n">
+      <c r="A29" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="36" t="n">
         <v>11904</v>
       </c>
-      <c r="C29" s="37" t="n">
+      <c r="C29" s="36" t="n">
         <v>4048</v>
       </c>
-      <c r="D29" s="37" t="n">
+      <c r="D29" s="36" t="n">
         <v>4416.65</v>
       </c>
-      <c r="E29" s="37" t="n">
+      <c r="E29" s="36" t="n">
         <v>7738</v>
       </c>
-      <c r="F29" s="37" t="n">
+      <c r="F29" s="36" t="n">
         <v>8000</v>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G29" s="36" t="n">
         <v>6200</v>
       </c>
-      <c r="H29" s="38"/>
-      <c r="I29" s="39" t="n">
+      <c r="H29" s="37"/>
+      <c r="I29" s="38" t="n">
         <f aca="false">MIN(E29:G29)</f>
         <v>6200</v>
       </c>
@@ -9673,37 +10243,44 @@
         <f aca="false">G29/$B29-1</f>
         <v>-0.479166666666667</v>
       </c>
-      <c r="Q29" s="40" t="n">
+      <c r="Q29" s="22" t="n">
+        <f aca="false">R29+S29</f>
         <v>6</v>
       </c>
-      <c r="R29" s="40" t="n">
+      <c r="R29" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="S29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="37" t="n">
+      <c r="A30" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="36" t="n">
         <v>4216</v>
       </c>
-      <c r="C30" s="37" t="n">
+      <c r="C30" s="36" t="n">
         <v>1104</v>
       </c>
-      <c r="D30" s="37" t="n">
+      <c r="D30" s="36" t="n">
         <v>1564.15</v>
       </c>
-      <c r="E30" s="37" t="n">
+      <c r="E30" s="36" t="n">
         <v>826</v>
       </c>
-      <c r="F30" s="37" t="n">
+      <c r="F30" s="36" t="n">
         <v>3000</v>
       </c>
-      <c r="G30" s="37" t="n">
+      <c r="G30" s="36" t="n">
         <v>1080</v>
       </c>
-      <c r="H30" s="38"/>
-      <c r="I30" s="39" t="n">
+      <c r="H30" s="37"/>
+      <c r="I30" s="38" t="n">
         <f aca="false">MIN(E30:G30)</f>
         <v>826</v>
       </c>
@@ -9732,37 +10309,44 @@
         <f aca="false">G30/$B30-1</f>
         <v>-0.743833017077799</v>
       </c>
-      <c r="Q30" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="40" t="n">
+      <c r="Q30" s="22" t="n">
+        <f aca="false">R30+S30</f>
+        <v>0</v>
+      </c>
+      <c r="R30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="37" t="n">
+      <c r="A31" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="36" t="n">
         <v>25684</v>
       </c>
-      <c r="C31" s="37" t="n">
+      <c r="C31" s="36" t="n">
         <v>4784</v>
       </c>
-      <c r="D31" s="37" t="n">
+      <c r="D31" s="36" t="n">
         <v>9528.75</v>
       </c>
-      <c r="E31" s="37" t="n">
+      <c r="E31" s="36" t="n">
         <v>16695</v>
       </c>
-      <c r="F31" s="37" t="n">
+      <c r="F31" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="G31" s="37" t="n">
+      <c r="G31" s="36" t="n">
         <v>18900</v>
       </c>
-      <c r="H31" s="38"/>
-      <c r="I31" s="39" t="n">
+      <c r="H31" s="37"/>
+      <c r="I31" s="38" t="n">
         <f aca="false">MIN(E31:G31)</f>
         <v>16695</v>
       </c>
@@ -9791,37 +10375,44 @@
         <f aca="false">G31/$B31-1</f>
         <v>-0.264133312568136</v>
       </c>
-      <c r="Q31" s="40" t="n">
+      <c r="Q31" s="22" t="n">
+        <f aca="false">R31+S31</f>
         <v>3</v>
       </c>
-      <c r="R31" s="40" t="n">
+      <c r="R31" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="37" t="n">
+      <c r="A32" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="36" t="n">
         <v>5137</v>
       </c>
-      <c r="C32" s="37" t="n">
+      <c r="C32" s="36" t="n">
         <v>368</v>
       </c>
-      <c r="D32" s="37" t="n">
+      <c r="D32" s="36" t="n">
         <v>1905.75</v>
       </c>
-      <c r="E32" s="37" t="n">
+      <c r="E32" s="36" t="n">
         <v>3339</v>
       </c>
-      <c r="F32" s="37" t="n">
+      <c r="F32" s="36" t="n">
         <v>3500</v>
       </c>
-      <c r="G32" s="37" t="n">
+      <c r="G32" s="36" t="n">
         <v>880</v>
       </c>
-      <c r="H32" s="38"/>
-      <c r="I32" s="39" t="n">
+      <c r="H32" s="37"/>
+      <c r="I32" s="38" t="n">
         <f aca="false">MIN(E32:G32)</f>
         <v>880</v>
       </c>
@@ -9850,37 +10441,44 @@
         <f aca="false">G32/$B32-1</f>
         <v>-0.828693790149893</v>
       </c>
-      <c r="Q32" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="40" t="n">
+      <c r="Q32" s="22" t="n">
+        <f aca="false">R32+S32</f>
+        <v>0</v>
+      </c>
+      <c r="R32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="37" t="n">
+      <c r="A33" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="36" t="n">
         <v>25419</v>
       </c>
-      <c r="C33" s="37" t="n">
+      <c r="C33" s="36" t="n">
         <v>8096</v>
       </c>
-      <c r="D33" s="37" t="n">
+      <c r="D33" s="36" t="n">
         <v>6565.3</v>
       </c>
-      <c r="E33" s="37" t="n">
+      <c r="E33" s="36" t="n">
         <v>11502</v>
       </c>
-      <c r="F33" s="37" t="n">
+      <c r="F33" s="36" t="n">
         <v>14000</v>
       </c>
-      <c r="G33" s="37" t="n">
+      <c r="G33" s="36" t="n">
         <v>7290</v>
       </c>
-      <c r="H33" s="38"/>
-      <c r="I33" s="39" t="n">
+      <c r="H33" s="37"/>
+      <c r="I33" s="38" t="n">
         <f aca="false">MIN(E33:G33)</f>
         <v>7290</v>
       </c>
@@ -9909,37 +10507,44 @@
         <f aca="false">G33/$B33-1</f>
         <v>-0.713206656438097</v>
       </c>
-      <c r="Q33" s="40" t="n">
+      <c r="Q33" s="22" t="n">
+        <f aca="false">R33+S33</f>
         <v>3</v>
       </c>
-      <c r="R33" s="40" t="n">
+      <c r="R33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="37" t="n">
+      <c r="A34" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="36" t="n">
         <v>17696</v>
       </c>
-      <c r="C34" s="37" t="n">
+      <c r="C34" s="36" t="n">
         <v>3312</v>
       </c>
-      <c r="D34" s="37" t="n">
+      <c r="D34" s="36" t="n">
         <v>9430.4</v>
       </c>
-      <c r="E34" s="37" t="n">
+      <c r="E34" s="36" t="n">
         <v>16522</v>
       </c>
-      <c r="F34" s="37" t="n">
+      <c r="F34" s="36" t="n">
         <v>20000</v>
       </c>
-      <c r="G34" s="37" t="n">
+      <c r="G34" s="36" t="n">
         <v>12150</v>
       </c>
-      <c r="H34" s="38"/>
-      <c r="I34" s="39" t="n">
+      <c r="H34" s="37"/>
+      <c r="I34" s="38" t="n">
         <f aca="false">MIN(E34:G34)</f>
         <v>12150</v>
       </c>
@@ -9968,37 +10573,44 @@
         <f aca="false">G34/$B34-1</f>
         <v>-0.313404159132007</v>
       </c>
-      <c r="Q34" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="40" t="n">
+      <c r="Q34" s="22" t="n">
+        <f aca="false">R34+S34</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" s="37" t="n">
+      <c r="A35" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="36" t="n">
         <v>40957</v>
       </c>
-      <c r="C35" s="37" t="n">
+      <c r="C35" s="36" t="n">
         <v>10672</v>
       </c>
-      <c r="D35" s="37" t="n">
+      <c r="D35" s="36" t="n">
         <v>15195.25</v>
       </c>
-      <c r="E35" s="37" t="n">
+      <c r="E35" s="36" t="n">
         <v>26622</v>
       </c>
-      <c r="F35" s="37" t="n">
+      <c r="F35" s="36" t="n">
         <v>30000</v>
       </c>
-      <c r="G35" s="37" t="n">
+      <c r="G35" s="36" t="n">
         <v>24300</v>
       </c>
-      <c r="H35" s="38"/>
-      <c r="I35" s="39" t="n">
+      <c r="H35" s="37"/>
+      <c r="I35" s="38" t="n">
         <f aca="false">MIN(E35:G35)</f>
         <v>24300</v>
       </c>
@@ -10027,37 +10639,44 @@
         <f aca="false">G35/$B35-1</f>
         <v>-0.406694826281222</v>
       </c>
-      <c r="Q35" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="40" t="n">
+      <c r="Q35" s="22" t="n">
+        <f aca="false">R35+S35</f>
+        <v>0</v>
+      </c>
+      <c r="R35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B36" s="37" t="n">
+      <c r="A36" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="36" t="n">
         <v>19364</v>
       </c>
-      <c r="C36" s="37" t="n">
+      <c r="C36" s="36" t="n">
         <v>552</v>
       </c>
-      <c r="D36" s="37" t="n">
+      <c r="D36" s="36" t="n">
         <v>7184.1</v>
       </c>
-      <c r="E36" s="37" t="n">
+      <c r="E36" s="36" t="n">
         <v>12587</v>
       </c>
-      <c r="F36" s="37" t="n">
+      <c r="F36" s="36" t="n">
         <v>9000</v>
       </c>
-      <c r="G36" s="37" t="n">
+      <c r="G36" s="36" t="n">
         <v>7800</v>
       </c>
-      <c r="H36" s="38"/>
-      <c r="I36" s="39" t="n">
+      <c r="H36" s="37"/>
+      <c r="I36" s="38" t="n">
         <f aca="false">MIN(E36:G36)</f>
         <v>7800</v>
       </c>
@@ -10086,37 +10705,44 @@
         <f aca="false">G36/$B36-1</f>
         <v>-0.597190663086139</v>
       </c>
-      <c r="Q36" s="40" t="n">
+      <c r="Q36" s="22" t="n">
+        <f aca="false">R36+S36</f>
         <v>1</v>
       </c>
-      <c r="R36" s="40" t="n">
+      <c r="R36" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="S36" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="37" t="n">
+      <c r="A37" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="36" t="n">
         <v>29043</v>
       </c>
-      <c r="C37" s="37" t="n">
+      <c r="C37" s="36" t="n">
         <v>1472</v>
       </c>
-      <c r="D37" s="37" t="n">
+      <c r="D37" s="36" t="n">
         <v>10774.75</v>
       </c>
-      <c r="E37" s="37" t="n">
+      <c r="E37" s="36" t="n">
         <v>18878</v>
       </c>
-      <c r="F37" s="37" t="n">
+      <c r="F37" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="G37" s="37" t="n">
+      <c r="G37" s="36" t="n">
         <v>11000</v>
       </c>
-      <c r="H37" s="38"/>
-      <c r="I37" s="39" t="n">
+      <c r="H37" s="37"/>
+      <c r="I37" s="38" t="n">
         <f aca="false">MIN(E37:G37)</f>
         <v>11000</v>
       </c>
@@ -10145,37 +10771,44 @@
         <f aca="false">G37/$B37-1</f>
         <v>-0.621251248149296</v>
       </c>
-      <c r="Q37" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="40" t="n">
+      <c r="Q37" s="22" t="n">
+        <f aca="false">R37+S37</f>
+        <v>0</v>
+      </c>
+      <c r="R37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="37" t="n">
+      <c r="A38" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="36" t="n">
         <v>29102</v>
       </c>
-      <c r="C38" s="37" t="n">
+      <c r="C38" s="36" t="n">
         <v>9568</v>
       </c>
-      <c r="D38" s="37" t="n">
+      <c r="D38" s="36" t="n">
         <v>10796.8</v>
       </c>
-      <c r="E38" s="37" t="n">
+      <c r="E38" s="36" t="n">
         <v>18916</v>
       </c>
-      <c r="F38" s="37" t="n">
+      <c r="F38" s="36" t="n">
         <v>24000</v>
       </c>
-      <c r="G38" s="37" t="n">
+      <c r="G38" s="36" t="n">
         <v>60000</v>
       </c>
-      <c r="H38" s="38"/>
-      <c r="I38" s="39" t="n">
+      <c r="H38" s="37"/>
+      <c r="I38" s="38" t="n">
         <f aca="false">MIN(E38:G38)</f>
         <v>18916</v>
       </c>
@@ -10204,37 +10837,44 @@
         <f aca="false">G38/$B38-1</f>
         <v>1.06171397154835</v>
       </c>
-      <c r="Q38" s="40" t="n">
+      <c r="Q38" s="22" t="n">
+        <f aca="false">R38+S38</f>
         <v>12</v>
       </c>
-      <c r="R38" s="40" t="n">
+      <c r="R38" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S38" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="22" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B39" s="37" t="n">
+      <c r="A39" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="36" t="n">
         <v>19364</v>
       </c>
-      <c r="C39" s="37" t="n">
+      <c r="C39" s="36" t="n">
         <v>2024</v>
       </c>
-      <c r="D39" s="37" t="n">
+      <c r="D39" s="36" t="n">
         <v>7184.1</v>
       </c>
-      <c r="E39" s="37" t="n">
+      <c r="E39" s="36" t="n">
         <v>12587</v>
       </c>
-      <c r="F39" s="37" t="n">
+      <c r="F39" s="36" t="n">
         <v>16000</v>
       </c>
-      <c r="G39" s="37" t="n">
+      <c r="G39" s="36" t="n">
         <v>12800</v>
       </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="39" t="n">
+      <c r="H39" s="37"/>
+      <c r="I39" s="38" t="n">
         <f aca="false">MIN(E39:G39)</f>
         <v>12587</v>
       </c>
@@ -10263,37 +10903,44 @@
         <f aca="false">G39/$B39-1</f>
         <v>-0.338979549679818</v>
       </c>
-      <c r="Q39" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" s="40" t="n">
+      <c r="Q39" s="22" t="n">
+        <f aca="false">R39+S39</f>
+        <v>0</v>
+      </c>
+      <c r="R39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="37" t="n">
+      <c r="A40" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="36" t="n">
         <v>29043</v>
       </c>
-      <c r="C40" s="37" t="n">
+      <c r="C40" s="36" t="n">
         <v>4784</v>
       </c>
-      <c r="D40" s="37" t="n">
+      <c r="D40" s="36" t="n">
         <v>10774.75</v>
       </c>
-      <c r="E40" s="37" t="n">
+      <c r="E40" s="36" t="n">
         <v>18878</v>
       </c>
-      <c r="F40" s="37" t="n">
+      <c r="F40" s="36" t="n">
         <v>24000</v>
       </c>
-      <c r="G40" s="37" t="n">
+      <c r="G40" s="36" t="n">
         <v>14000</v>
       </c>
-      <c r="H40" s="38"/>
-      <c r="I40" s="39" t="n">
+      <c r="H40" s="37"/>
+      <c r="I40" s="38" t="n">
         <f aca="false">MIN(E40:G40)</f>
         <v>14000</v>
       </c>
@@ -10322,37 +10969,44 @@
         <f aca="false">G40/$B40-1</f>
         <v>-0.517956134008195</v>
       </c>
-      <c r="Q40" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="40" t="n">
+      <c r="Q40" s="22" t="n">
+        <f aca="false">R40+S40</f>
+        <v>0</v>
+      </c>
+      <c r="R40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="37" t="n">
+      <c r="A41" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="36" t="n">
         <v>12093</v>
       </c>
-      <c r="C41" s="37" t="n">
+      <c r="C41" s="36" t="n">
         <v>2024</v>
       </c>
-      <c r="D41" s="37" t="n">
+      <c r="D41" s="36" t="n">
         <v>4486.3</v>
       </c>
-      <c r="E41" s="37" t="n">
+      <c r="E41" s="36" t="n">
         <v>8463</v>
       </c>
-      <c r="F41" s="37" t="n">
+      <c r="F41" s="36" t="n">
         <v>11000</v>
       </c>
-      <c r="G41" s="37" t="n">
+      <c r="G41" s="36" t="n">
         <v>7800</v>
       </c>
-      <c r="H41" s="38"/>
-      <c r="I41" s="39" t="n">
+      <c r="H41" s="37"/>
+      <c r="I41" s="38" t="n">
         <f aca="false">MIN(E41:G41)</f>
         <v>7800</v>
       </c>
@@ -10381,37 +11035,44 @@
         <f aca="false">G41/$B41-1</f>
         <v>-0.354998759612999</v>
       </c>
-      <c r="Q41" s="40" t="n">
+      <c r="Q41" s="22" t="n">
+        <f aca="false">R41+S41</f>
         <v>4</v>
       </c>
-      <c r="R41" s="40" t="n">
+      <c r="R41" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S41" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="B42" s="37" t="n">
+      <c r="A42" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="36" t="n">
         <v>5678</v>
       </c>
-      <c r="C42" s="37" t="n">
+      <c r="C42" s="36" t="n">
         <v>1288</v>
       </c>
-      <c r="D42" s="37" t="n">
+      <c r="D42" s="36" t="n">
         <v>2106.3</v>
       </c>
-      <c r="E42" s="37" t="n">
+      <c r="E42" s="36" t="n">
         <v>3691</v>
       </c>
-      <c r="F42" s="37" t="n">
+      <c r="F42" s="36" t="n">
         <v>4500</v>
       </c>
-      <c r="G42" s="37" t="n">
+      <c r="G42" s="36" t="n">
         <v>4860</v>
       </c>
-      <c r="H42" s="38"/>
-      <c r="I42" s="39" t="n">
+      <c r="H42" s="37"/>
+      <c r="I42" s="38" t="n">
         <f aca="false">MIN(E42:G42)</f>
         <v>3691</v>
       </c>
@@ -10440,37 +11101,44 @@
         <f aca="false">G42/$B42-1</f>
         <v>-0.144064811553364</v>
       </c>
-      <c r="Q42" s="40" t="n">
+      <c r="Q42" s="22" t="n">
+        <f aca="false">R42+S42</f>
+        <v>40</v>
+      </c>
+      <c r="R42" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="40" t="n">
+      <c r="S42" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="T42" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="B43" s="37" t="n">
+      <c r="A43" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="36" t="n">
         <v>13020</v>
       </c>
-      <c r="C43" s="37" t="n">
+      <c r="C43" s="36" t="n">
         <v>2208</v>
       </c>
-      <c r="D43" s="37" t="n">
+      <c r="D43" s="36" t="n">
         <v>4830.7</v>
       </c>
-      <c r="E43" s="37" t="n">
+      <c r="E43" s="36" t="n">
         <v>8463</v>
       </c>
-      <c r="F43" s="37" t="n">
+      <c r="F43" s="36" t="n">
         <v>1000</v>
       </c>
-      <c r="G43" s="37" t="n">
+      <c r="G43" s="36" t="n">
         <v>5400</v>
       </c>
-      <c r="H43" s="38"/>
-      <c r="I43" s="39" t="n">
+      <c r="H43" s="37"/>
+      <c r="I43" s="38" t="n">
         <f aca="false">MIN(E43:G43)</f>
         <v>1000</v>
       </c>
@@ -10499,37 +11167,44 @@
         <f aca="false">G43/$B43-1</f>
         <v>-0.585253456221198</v>
       </c>
-      <c r="Q43" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="40" t="n">
+      <c r="Q43" s="22" t="n">
+        <f aca="false">R43+S43</f>
+        <v>0</v>
+      </c>
+      <c r="R43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B44" s="37" t="n">
+      <c r="A44" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="36" t="n">
         <v>117535</v>
       </c>
-      <c r="C44" s="37" t="n">
+      <c r="C44" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="D44" s="37" t="n">
+      <c r="D44" s="36" t="n">
         <v>43605.45</v>
       </c>
-      <c r="E44" s="37" t="n">
+      <c r="E44" s="36" t="n">
         <v>76398</v>
       </c>
-      <c r="F44" s="37" t="n">
+      <c r="F44" s="36" t="n">
         <v>85000</v>
       </c>
-      <c r="G44" s="37" t="n">
+      <c r="G44" s="36" t="n">
         <v>65000</v>
       </c>
-      <c r="H44" s="38"/>
-      <c r="I44" s="39" t="n">
+      <c r="H44" s="37"/>
+      <c r="I44" s="38" t="n">
         <f aca="false">MIN(E44:G44)</f>
         <v>65000</v>
       </c>
@@ -10558,37 +11233,44 @@
         <f aca="false">G44/$B44-1</f>
         <v>-0.446973242013017</v>
       </c>
-      <c r="Q44" s="40" t="n">
+      <c r="Q44" s="22" t="n">
+        <f aca="false">R44+S44</f>
         <v>1</v>
       </c>
-      <c r="R44" s="40" t="n">
+      <c r="R44" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="S44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="37" t="n">
+      <c r="A45" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="36" t="n">
         <v>22729</v>
       </c>
-      <c r="C45" s="37" t="n">
+      <c r="C45" s="36" t="n">
         <v>3864</v>
       </c>
-      <c r="D45" s="37" t="n">
+      <c r="D45" s="36" t="n">
         <v>8432.55</v>
       </c>
-      <c r="E45" s="37" t="n">
+      <c r="E45" s="36" t="n">
         <v>14774</v>
       </c>
-      <c r="F45" s="37" t="n">
+      <c r="F45" s="36" t="n">
         <v>15000</v>
       </c>
-      <c r="G45" s="37" t="n">
+      <c r="G45" s="36" t="n">
         <v>18000</v>
       </c>
-      <c r="H45" s="38"/>
-      <c r="I45" s="39" t="n">
+      <c r="H45" s="37"/>
+      <c r="I45" s="38" t="n">
         <f aca="false">MIN(E45:G45)</f>
         <v>14774</v>
       </c>
@@ -10617,37 +11299,44 @@
         <f aca="false">G45/$B45-1</f>
         <v>-0.208060187425756</v>
       </c>
-      <c r="Q45" s="40" t="n">
+      <c r="Q45" s="22" t="n">
+        <f aca="false">R45+S45</f>
         <v>5</v>
       </c>
-      <c r="R45" s="40" t="n">
+      <c r="R45" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46" s="37" t="n">
+      <c r="A46" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="36" t="n">
         <v>27699</v>
       </c>
-      <c r="C46" s="37" t="n">
+      <c r="C46" s="36" t="n">
         <v>1014</v>
       </c>
-      <c r="D46" s="37" t="n">
+      <c r="D46" s="36" t="n">
         <v>10276.35</v>
       </c>
-      <c r="E46" s="37" t="n">
+      <c r="E46" s="36" t="n">
         <v>18004</v>
       </c>
-      <c r="F46" s="37" t="n">
+      <c r="F46" s="36" t="n">
         <v>20000</v>
       </c>
-      <c r="G46" s="37" t="n">
+      <c r="G46" s="36" t="n">
         <v>22000</v>
       </c>
-      <c r="H46" s="38"/>
-      <c r="I46" s="39" t="n">
+      <c r="H46" s="37"/>
+      <c r="I46" s="38" t="n">
         <f aca="false">MIN(E46:G46)</f>
         <v>18004</v>
       </c>
@@ -10676,37 +11365,44 @@
         <f aca="false">G46/$B46-1</f>
         <v>-0.205747499909744</v>
       </c>
-      <c r="Q46" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="40" t="n">
+      <c r="Q46" s="22" t="n">
+        <f aca="false">R46+S46</f>
+        <v>0</v>
+      </c>
+      <c r="R46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" s="37" t="n">
+      <c r="A47" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="36" t="n">
         <v>2598</v>
       </c>
-      <c r="C47" s="37" t="n">
+      <c r="C47" s="36" t="n">
         <v>1067.2</v>
       </c>
-      <c r="D47" s="37" t="n">
+      <c r="D47" s="36" t="n">
         <v>963.9</v>
       </c>
-      <c r="E47" s="37" t="n">
+      <c r="E47" s="36" t="n">
         <v>1689</v>
       </c>
-      <c r="F47" s="37" t="n">
+      <c r="F47" s="36" t="n">
         <v>2000</v>
       </c>
-      <c r="G47" s="37" t="n">
+      <c r="G47" s="36" t="n">
         <v>1800</v>
       </c>
-      <c r="H47" s="38"/>
-      <c r="I47" s="39" t="n">
+      <c r="H47" s="37"/>
+      <c r="I47" s="38" t="n">
         <f aca="false">MIN(E47:G47)</f>
         <v>1689</v>
       </c>
@@ -10735,37 +11431,44 @@
         <f aca="false">G47/$B47-1</f>
         <v>-0.30715935334873</v>
       </c>
-      <c r="Q47" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="40" t="n">
+      <c r="Q47" s="22" t="n">
+        <f aca="false">R47+S47</f>
+        <v>0</v>
+      </c>
+      <c r="R47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="B48" s="37" t="n">
+      <c r="A48" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="36" t="n">
         <v>18296</v>
       </c>
-      <c r="C48" s="37" t="n">
+      <c r="C48" s="36" t="n">
         <v>8500</v>
       </c>
-      <c r="D48" s="37" t="n">
+      <c r="D48" s="36" t="n">
         <v>6787.9</v>
       </c>
-      <c r="E48" s="37" t="n">
+      <c r="E48" s="36" t="n">
         <v>11892</v>
       </c>
-      <c r="F48" s="37" t="n">
+      <c r="F48" s="36" t="n">
         <v>15000</v>
       </c>
-      <c r="G48" s="37" t="n">
+      <c r="G48" s="36" t="n">
         <v>14700</v>
       </c>
-      <c r="H48" s="38"/>
-      <c r="I48" s="39" t="n">
+      <c r="H48" s="37"/>
+      <c r="I48" s="38" t="n">
         <f aca="false">MIN(E48:G48)</f>
         <v>11892</v>
       </c>
@@ -10794,37 +11497,44 @@
         <f aca="false">G48/$B48-1</f>
         <v>-0.196545693047661</v>
       </c>
-      <c r="Q48" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="40" t="n">
+      <c r="Q48" s="22" t="n">
+        <f aca="false">R48+S48</f>
+        <v>0</v>
+      </c>
+      <c r="R48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="37" t="n">
+      <c r="A49" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="36" t="n">
         <v>7858</v>
       </c>
-      <c r="C49" s="37" t="n">
+      <c r="C49" s="36" t="n">
         <v>7500</v>
       </c>
-      <c r="D49" s="37" t="n">
+      <c r="D49" s="36" t="n">
         <v>4239.2</v>
       </c>
-      <c r="E49" s="37" t="n">
+      <c r="E49" s="36" t="n">
         <v>6035</v>
       </c>
-      <c r="F49" s="37" t="n">
+      <c r="F49" s="36" t="n">
         <v>7000</v>
       </c>
-      <c r="G49" s="37" t="n">
+      <c r="G49" s="36" t="n">
         <v>8800</v>
       </c>
-      <c r="H49" s="38"/>
-      <c r="I49" s="39" t="n">
+      <c r="H49" s="37"/>
+      <c r="I49" s="38" t="n">
         <f aca="false">MIN(E49:G49)</f>
         <v>6035</v>
       </c>
@@ -10853,37 +11563,44 @@
         <f aca="false">G49/$B49-1</f>
         <v>0.11987783150929</v>
       </c>
-      <c r="Q49" s="40" t="n">
+      <c r="Q49" s="22" t="n">
+        <f aca="false">R49+S49</f>
         <v>6</v>
       </c>
-      <c r="R49" s="40" t="n">
+      <c r="R49" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="B50" s="37" t="n">
+      <c r="A50" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="36" t="n">
         <v>7030</v>
       </c>
-      <c r="C50" s="37" t="n">
+      <c r="C50" s="36" t="n">
         <v>2208</v>
       </c>
-      <c r="D50" s="37" t="n">
+      <c r="D50" s="36" t="n">
         <v>2608.2</v>
       </c>
-      <c r="E50" s="37" t="n">
+      <c r="E50" s="36" t="n">
         <v>4570</v>
       </c>
-      <c r="F50" s="37" t="n">
+      <c r="F50" s="36" t="n">
         <v>5500</v>
       </c>
-      <c r="G50" s="37" t="n">
+      <c r="G50" s="36" t="n">
         <v>3400</v>
       </c>
-      <c r="H50" s="38"/>
-      <c r="I50" s="39" t="n">
+      <c r="H50" s="37"/>
+      <c r="I50" s="38" t="n">
         <f aca="false">MIN(E50:G50)</f>
         <v>3400</v>
       </c>
@@ -10912,37 +11629,44 @@
         <f aca="false">G50/$B50-1</f>
         <v>-0.516358463726885</v>
       </c>
-      <c r="Q50" s="40" t="n">
+      <c r="Q50" s="22" t="n">
+        <f aca="false">R50+S50</f>
         <v>3</v>
       </c>
-      <c r="R50" s="40" t="n">
+      <c r="R50" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B51" s="37" t="n">
+      <c r="A51" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="36" t="n">
         <v>1556</v>
       </c>
-      <c r="C51" s="37" t="n">
+      <c r="C51" s="36" t="n">
         <v>367</v>
       </c>
-      <c r="D51" s="37" t="n">
+      <c r="D51" s="36" t="n">
         <v>577.15</v>
       </c>
-      <c r="E51" s="37" t="n">
+      <c r="E51" s="36" t="n">
         <v>1011</v>
       </c>
-      <c r="F51" s="37" t="n">
+      <c r="F51" s="36" t="n">
         <v>1000</v>
       </c>
-      <c r="G51" s="37" t="n">
+      <c r="G51" s="36" t="n">
         <v>523.26</v>
       </c>
-      <c r="H51" s="38"/>
-      <c r="I51" s="39" t="n">
+      <c r="H51" s="37"/>
+      <c r="I51" s="38" t="n">
         <f aca="false">MIN(E51:G51)</f>
         <v>523.26</v>
       </c>
@@ -10971,37 +11695,44 @@
         <f aca="false">G51/$B51-1</f>
         <v>-0.663714652956298</v>
       </c>
-      <c r="Q51" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="40" t="n">
+      <c r="Q51" s="22" t="n">
+        <f aca="false">R51+S51</f>
+        <v>0</v>
+      </c>
+      <c r="R51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="37" t="n">
+      <c r="A52" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="36" t="n">
         <v>1040</v>
       </c>
-      <c r="C52" s="37" t="n">
+      <c r="C52" s="36" t="n">
         <v>263</v>
       </c>
-      <c r="D52" s="37" t="n">
+      <c r="D52" s="36" t="n">
         <v>385.7</v>
       </c>
-      <c r="E52" s="37" t="n">
+      <c r="E52" s="36" t="n">
         <v>676</v>
       </c>
-      <c r="F52" s="37" t="n">
+      <c r="F52" s="36" t="n">
         <v>600</v>
       </c>
-      <c r="G52" s="37" t="n">
+      <c r="G52" s="36" t="n">
         <v>361.25</v>
       </c>
-      <c r="H52" s="38"/>
-      <c r="I52" s="39" t="n">
+      <c r="H52" s="37"/>
+      <c r="I52" s="38" t="n">
         <f aca="false">MIN(E52:G52)</f>
         <v>361.25</v>
       </c>
@@ -11030,37 +11761,44 @@
         <f aca="false">G52/$B52-1</f>
         <v>-0.652644230769231</v>
       </c>
-      <c r="Q52" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" s="40" t="n">
+      <c r="Q52" s="22" t="n">
+        <f aca="false">R52+S52</f>
+        <v>0</v>
+      </c>
+      <c r="R52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B53" s="37" t="n">
+      <c r="A53" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="36" t="n">
         <v>727</v>
       </c>
-      <c r="C53" s="37" t="n">
+      <c r="C53" s="36" t="n">
         <v>127</v>
       </c>
-      <c r="D53" s="37" t="n">
+      <c r="D53" s="36" t="n">
         <v>269.5</v>
       </c>
-      <c r="E53" s="37" t="n">
+      <c r="E53" s="36" t="n">
         <v>473</v>
       </c>
-      <c r="F53" s="37" t="n">
+      <c r="F53" s="36" t="n">
         <v>300</v>
       </c>
-      <c r="G53" s="37" t="n">
+      <c r="G53" s="36" t="n">
         <v>201.42</v>
       </c>
-      <c r="H53" s="38"/>
-      <c r="I53" s="39" t="n">
+      <c r="H53" s="37"/>
+      <c r="I53" s="38" t="n">
         <f aca="false">MIN(E53:G53)</f>
         <v>201.42</v>
       </c>
@@ -11089,37 +11827,44 @@
         <f aca="false">G53/$B53-1</f>
         <v>-0.722943603851444</v>
       </c>
-      <c r="Q53" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" s="40" t="n">
+      <c r="Q53" s="22" t="n">
+        <f aca="false">R53+S53</f>
+        <v>0</v>
+      </c>
+      <c r="R53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B54" s="37" t="n">
+      <c r="A54" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="36" t="n">
         <v>779</v>
       </c>
-      <c r="C54" s="37" t="n">
+      <c r="C54" s="36" t="n">
         <v>460</v>
       </c>
-      <c r="D54" s="37" t="n">
+      <c r="D54" s="36" t="n">
         <v>288.75</v>
       </c>
-      <c r="E54" s="37" t="n">
+      <c r="E54" s="36" t="n">
         <v>506</v>
       </c>
-      <c r="F54" s="37" t="n">
+      <c r="F54" s="36" t="n">
         <v>600</v>
       </c>
-      <c r="G54" s="37" t="n">
+      <c r="G54" s="36" t="n">
         <v>650</v>
       </c>
-      <c r="H54" s="38"/>
-      <c r="I54" s="39" t="n">
+      <c r="H54" s="37"/>
+      <c r="I54" s="38" t="n">
         <f aca="false">MIN(E54:G54)</f>
         <v>506</v>
       </c>
@@ -11148,37 +11893,44 @@
         <f aca="false">G54/$B54-1</f>
         <v>-0.165596919127086</v>
       </c>
-      <c r="Q54" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="40" t="n">
+      <c r="Q54" s="22" t="n">
+        <f aca="false">R54+S54</f>
+        <v>0</v>
+      </c>
+      <c r="R54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" s="37" t="n">
+      <c r="A55" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" s="36" t="n">
         <v>39000</v>
       </c>
-      <c r="C55" s="37" t="n">
+      <c r="C55" s="36" t="n">
         <v>120000</v>
       </c>
-      <c r="D55" s="37" t="n">
+      <c r="D55" s="36" t="n">
         <v>68000</v>
       </c>
-      <c r="E55" s="37" t="n">
+      <c r="E55" s="36" t="n">
         <v>42070</v>
       </c>
-      <c r="F55" s="37" t="n">
+      <c r="F55" s="36" t="n">
         <v>86000</v>
       </c>
-      <c r="G55" s="37" t="n">
+      <c r="G55" s="36" t="n">
         <v>139927</v>
       </c>
-      <c r="H55" s="38"/>
-      <c r="I55" s="39" t="n">
+      <c r="H55" s="37"/>
+      <c r="I55" s="38" t="n">
         <f aca="false">MIN(E55:G55)</f>
         <v>42070</v>
       </c>
@@ -11207,43 +11959,50 @@
         <f aca="false">G55</f>
         <v>139927</v>
       </c>
-      <c r="Q55" s="40" t="n">
+      <c r="Q55" s="22" t="n">
+        <f aca="false">R55+S55</f>
         <v>12</v>
       </c>
-      <c r="R55" s="40" t="n">
+      <c r="R55" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="S55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="B56" s="42" t="n">
+        <v>89</v>
+      </c>
+      <c r="B56" s="40" t="n">
         <f aca="false">SUM(B2:B55)</f>
         <v>1096326</v>
       </c>
-      <c r="C56" s="42" t="n">
+      <c r="C56" s="40" t="n">
         <f aca="false">SUM(C2:C55)</f>
         <v>341277.2</v>
       </c>
-      <c r="D56" s="42" t="n">
+      <c r="D56" s="40" t="n">
         <f aca="false">SUM(D2:D55)</f>
         <v>394854.15</v>
       </c>
-      <c r="E56" s="42" t="n">
+      <c r="E56" s="40" t="n">
         <f aca="false">SUM(E2:E55)</f>
         <v>622951</v>
       </c>
-      <c r="F56" s="42" t="n">
+      <c r="F56" s="40" t="n">
         <f aca="false">SUM(F2:F55)</f>
         <v>704000</v>
       </c>
-      <c r="G56" s="42" t="n">
+      <c r="G56" s="40" t="n">
         <f aca="false">SUM(G2:G55)</f>
         <v>773484.6</v>
       </c>
-      <c r="H56" s="42"/>
-      <c r="I56" s="43" t="n">
+      <c r="H56" s="40"/>
+      <c r="I56" s="41" t="n">
         <f aca="false">SUM(I2:I55)</f>
         <v>531072.93</v>
       </c>
